--- a/packages/server/src/arpa_reporter/data/treasury/project519521BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project519521BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JohnsonTa\Desktop\SLFRF Templates\SLFRF Q2 2026 Updates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125CA513-F428-48C2-86D8-E8BF8BC5802D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B471C7E-EE62-47F0-BAF7-AF22D01D24CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="90" windowWidth="28800" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1545" windowWidth="22747" windowHeight="12277" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -688,10 +688,10 @@
 "No"</t>
   </si>
   <si>
-    <t>Q2_2026_Obligations__c</t>
+    <t>Q3_2026_Obligations__c</t>
   </si>
   <si>
-    <t>Q2_2026_Expenditures__c</t>
+    <t>Q3_2026_Expenditures__c</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE1000"/>
-  <sheetFormatPr defaultColWidth="23.375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="23.375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="7" width="23.375" style="2"/>
     <col min="8" max="9" width="35.5" style="2" customWidth="1"/>
@@ -1164,7 +1164,7 @@
     <col min="58" max="16384" width="23.375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>142</v>
       </c>
@@ -1223,7 +1223,7 @@
       <c r="BD1" s="4"/>
       <c r="BE1" s="4"/>
     </row>
-    <row r="2" spans="1:57" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:57" ht="38.25" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>35</v>
       </c>
@@ -1282,7 +1282,7 @@
       <c r="BD2" s="4"/>
       <c r="BE2" s="4"/>
     </row>
-    <row r="3" spans="1:57" ht="213.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:57" ht="213.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>34</v>
       </c>
@@ -1341,7 +1341,7 @@
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
     </row>
-    <row r="4" spans="1:57" s="4" customFormat="1" ht="70.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:57" s="4" customFormat="1" ht="70.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="216.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:57" ht="229.5" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:57" s="9" customFormat="1" ht="178.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:57" s="9" customFormat="1" ht="178.5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="96.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:57" ht="96.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2057,7 +2057,7 @@
       <c r="BD8" s="4"/>
       <c r="BE8" s="4"/>
     </row>
-    <row r="9" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2081,7 +2081,7 @@
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
     </row>
-    <row r="10" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2105,7 +2105,7 @@
       <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
     </row>
-    <row r="11" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2129,7 +2129,7 @@
       <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
     </row>
-    <row r="12" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2153,7 +2153,7 @@
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
     </row>
-    <row r="13" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2177,7 +2177,7 @@
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
     </row>
-    <row r="14" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -2201,7 +2201,7 @@
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
     </row>
-    <row r="15" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2225,7 +2225,7 @@
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
     </row>
-    <row r="16" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2249,7 +2249,7 @@
       <c r="BD16" s="4"/>
       <c r="BE16" s="4"/>
     </row>
-    <row r="17" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2273,7 +2273,7 @@
       <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
     </row>
-    <row r="18" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2297,7 +2297,7 @@
       <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
     </row>
-    <row r="19" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2321,7 +2321,7 @@
       <c r="BD19" s="4"/>
       <c r="BE19" s="4"/>
     </row>
-    <row r="20" spans="1:57" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2345,7 +2345,7 @@
       <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
     </row>
-    <row r="21" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2369,7 +2369,7 @@
       <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
     </row>
-    <row r="22" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2393,7 +2393,7 @@
       <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
     </row>
-    <row r="23" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2417,7 +2417,7 @@
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
     </row>
-    <row r="24" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -2441,7 +2441,7 @@
       <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
     </row>
-    <row r="25" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2465,7 +2465,7 @@
       <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
     </row>
-    <row r="26" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2489,7 +2489,7 @@
       <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
     </row>
-    <row r="27" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2513,7 +2513,7 @@
       <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
     </row>
-    <row r="28" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2537,7 +2537,7 @@
       <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
     </row>
-    <row r="29" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2561,7 +2561,7 @@
       <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
     </row>
-    <row r="30" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2585,7 +2585,7 @@
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
     </row>
-    <row r="31" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2609,7 +2609,7 @@
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
     </row>
-    <row r="32" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2633,7 +2633,7 @@
       <c r="BD32" s="4"/>
       <c r="BE32" s="4"/>
     </row>
-    <row r="33" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2657,7 +2657,7 @@
       <c r="BD33" s="4"/>
       <c r="BE33" s="4"/>
     </row>
-    <row r="34" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2681,7 +2681,7 @@
       <c r="BD34" s="4"/>
       <c r="BE34" s="4"/>
     </row>
-    <row r="35" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2705,7 +2705,7 @@
       <c r="BD35" s="4"/>
       <c r="BE35" s="4"/>
     </row>
-    <row r="36" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2729,7 +2729,7 @@
       <c r="BD36" s="4"/>
       <c r="BE36" s="4"/>
     </row>
-    <row r="37" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2753,7 +2753,7 @@
       <c r="BD37" s="4"/>
       <c r="BE37" s="4"/>
     </row>
-    <row r="38" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2777,7 +2777,7 @@
       <c r="BD38" s="4"/>
       <c r="BE38" s="4"/>
     </row>
-    <row r="39" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2801,7 +2801,7 @@
       <c r="BD39" s="4"/>
       <c r="BE39" s="4"/>
     </row>
-    <row r="40" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2825,7 +2825,7 @@
       <c r="BD40" s="4"/>
       <c r="BE40" s="4"/>
     </row>
-    <row r="41" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2849,7 +2849,7 @@
       <c r="BD41" s="4"/>
       <c r="BE41" s="4"/>
     </row>
-    <row r="42" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2873,7 +2873,7 @@
       <c r="BD42" s="4"/>
       <c r="BE42" s="4"/>
     </row>
-    <row r="43" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -2897,7 +2897,7 @@
       <c r="BD43" s="4"/>
       <c r="BE43" s="4"/>
     </row>
-    <row r="44" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2921,7 +2921,7 @@
       <c r="BD44" s="4"/>
       <c r="BE44" s="4"/>
     </row>
-    <row r="45" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2945,7 +2945,7 @@
       <c r="BD45" s="4"/>
       <c r="BE45" s="4"/>
     </row>
-    <row r="46" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2969,7 +2969,7 @@
       <c r="BD46" s="4"/>
       <c r="BE46" s="4"/>
     </row>
-    <row r="47" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2993,7 +2993,7 @@
       <c r="BD47" s="4"/>
       <c r="BE47" s="4"/>
     </row>
-    <row r="48" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3017,7 +3017,7 @@
       <c r="BD48" s="4"/>
       <c r="BE48" s="4"/>
     </row>
-    <row r="49" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3041,7 +3041,7 @@
       <c r="BD49" s="4"/>
       <c r="BE49" s="4"/>
     </row>
-    <row r="50" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3065,7 +3065,7 @@
       <c r="BD50" s="4"/>
       <c r="BE50" s="4"/>
     </row>
-    <row r="51" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3089,7 +3089,7 @@
       <c r="BD51" s="4"/>
       <c r="BE51" s="4"/>
     </row>
-    <row r="52" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3113,7 +3113,7 @@
       <c r="BD52" s="4"/>
       <c r="BE52" s="4"/>
     </row>
-    <row r="53" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3137,7 +3137,7 @@
       <c r="BD53" s="4"/>
       <c r="BE53" s="4"/>
     </row>
-    <row r="54" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3161,7 +3161,7 @@
       <c r="BD54" s="4"/>
       <c r="BE54" s="4"/>
     </row>
-    <row r="55" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3185,7 +3185,7 @@
       <c r="BD55" s="4"/>
       <c r="BE55" s="4"/>
     </row>
-    <row r="56" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3209,7 +3209,7 @@
       <c r="BD56" s="4"/>
       <c r="BE56" s="4"/>
     </row>
-    <row r="57" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3233,7 +3233,7 @@
       <c r="BD57" s="4"/>
       <c r="BE57" s="4"/>
     </row>
-    <row r="58" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3257,7 +3257,7 @@
       <c r="BD58" s="4"/>
       <c r="BE58" s="4"/>
     </row>
-    <row r="59" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3281,7 +3281,7 @@
       <c r="BD59" s="4"/>
       <c r="BE59" s="4"/>
     </row>
-    <row r="60" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3305,7 +3305,7 @@
       <c r="BD60" s="4"/>
       <c r="BE60" s="4"/>
     </row>
-    <row r="61" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3329,7 +3329,7 @@
       <c r="BD61" s="4"/>
       <c r="BE61" s="4"/>
     </row>
-    <row r="62" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3353,7 +3353,7 @@
       <c r="BD62" s="4"/>
       <c r="BE62" s="4"/>
     </row>
-    <row r="63" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3377,7 +3377,7 @@
       <c r="BD63" s="4"/>
       <c r="BE63" s="4"/>
     </row>
-    <row r="64" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3401,7 +3401,7 @@
       <c r="BD64" s="4"/>
       <c r="BE64" s="4"/>
     </row>
-    <row r="65" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3425,7 +3425,7 @@
       <c r="BD65" s="4"/>
       <c r="BE65" s="4"/>
     </row>
-    <row r="66" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3449,7 +3449,7 @@
       <c r="BD66" s="4"/>
       <c r="BE66" s="4"/>
     </row>
-    <row r="67" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3473,7 +3473,7 @@
       <c r="BD67" s="4"/>
       <c r="BE67" s="4"/>
     </row>
-    <row r="68" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3497,7 +3497,7 @@
       <c r="BD68" s="4"/>
       <c r="BE68" s="4"/>
     </row>
-    <row r="69" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3521,7 +3521,7 @@
       <c r="BD69" s="4"/>
       <c r="BE69" s="4"/>
     </row>
-    <row r="70" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3545,7 +3545,7 @@
       <c r="BD70" s="4"/>
       <c r="BE70" s="4"/>
     </row>
-    <row r="71" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3569,7 +3569,7 @@
       <c r="BD71" s="4"/>
       <c r="BE71" s="4"/>
     </row>
-    <row r="72" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3593,7 +3593,7 @@
       <c r="BD72" s="4"/>
       <c r="BE72" s="4"/>
     </row>
-    <row r="73" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3617,7 +3617,7 @@
       <c r="BD73" s="4"/>
       <c r="BE73" s="4"/>
     </row>
-    <row r="74" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3641,7 +3641,7 @@
       <c r="BD74" s="4"/>
       <c r="BE74" s="4"/>
     </row>
-    <row r="75" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3665,7 +3665,7 @@
       <c r="BD75" s="4"/>
       <c r="BE75" s="4"/>
     </row>
-    <row r="76" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3689,7 +3689,7 @@
       <c r="BD76" s="4"/>
       <c r="BE76" s="4"/>
     </row>
-    <row r="77" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3713,7 +3713,7 @@
       <c r="BD77" s="4"/>
       <c r="BE77" s="4"/>
     </row>
-    <row r="78" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3737,7 +3737,7 @@
       <c r="BD78" s="4"/>
       <c r="BE78" s="4"/>
     </row>
-    <row r="79" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3761,7 +3761,7 @@
       <c r="BD79" s="4"/>
       <c r="BE79" s="4"/>
     </row>
-    <row r="80" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3785,7 +3785,7 @@
       <c r="BD80" s="4"/>
       <c r="BE80" s="4"/>
     </row>
-    <row r="81" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3809,7 +3809,7 @@
       <c r="BD81" s="4"/>
       <c r="BE81" s="4"/>
     </row>
-    <row r="82" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3833,7 +3833,7 @@
       <c r="BD82" s="4"/>
       <c r="BE82" s="4"/>
     </row>
-    <row r="83" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3857,7 +3857,7 @@
       <c r="BD83" s="4"/>
       <c r="BE83" s="4"/>
     </row>
-    <row r="84" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3881,7 +3881,7 @@
       <c r="BD84" s="4"/>
       <c r="BE84" s="4"/>
     </row>
-    <row r="85" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3905,7 +3905,7 @@
       <c r="BD85" s="4"/>
       <c r="BE85" s="4"/>
     </row>
-    <row r="86" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3929,7 +3929,7 @@
       <c r="BD86" s="4"/>
       <c r="BE86" s="4"/>
     </row>
-    <row r="87" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3953,7 +3953,7 @@
       <c r="BD87" s="4"/>
       <c r="BE87" s="4"/>
     </row>
-    <row r="88" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3977,7 +3977,7 @@
       <c r="BD88" s="4"/>
       <c r="BE88" s="4"/>
     </row>
-    <row r="89" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4001,7 +4001,7 @@
       <c r="BD89" s="4"/>
       <c r="BE89" s="4"/>
     </row>
-    <row r="90" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4025,7 +4025,7 @@
       <c r="BD90" s="4"/>
       <c r="BE90" s="4"/>
     </row>
-    <row r="91" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4049,7 +4049,7 @@
       <c r="BD91" s="4"/>
       <c r="BE91" s="4"/>
     </row>
-    <row r="92" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4073,7 +4073,7 @@
       <c r="BD92" s="4"/>
       <c r="BE92" s="4"/>
     </row>
-    <row r="93" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4097,7 +4097,7 @@
       <c r="BD93" s="4"/>
       <c r="BE93" s="4"/>
     </row>
-    <row r="94" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4121,7 +4121,7 @@
       <c r="BD94" s="4"/>
       <c r="BE94" s="4"/>
     </row>
-    <row r="95" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4145,7 +4145,7 @@
       <c r="BD95" s="4"/>
       <c r="BE95" s="4"/>
     </row>
-    <row r="96" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4169,7 +4169,7 @@
       <c r="BD96" s="4"/>
       <c r="BE96" s="4"/>
     </row>
-    <row r="97" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4193,7 +4193,7 @@
       <c r="BD97" s="4"/>
       <c r="BE97" s="4"/>
     </row>
-    <row r="98" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4217,7 +4217,7 @@
       <c r="BD98" s="4"/>
       <c r="BE98" s="4"/>
     </row>
-    <row r="99" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4241,7 +4241,7 @@
       <c r="BD99" s="4"/>
       <c r="BE99" s="4"/>
     </row>
-    <row r="100" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4265,7 +4265,7 @@
       <c r="BD100" s="4"/>
       <c r="BE100" s="4"/>
     </row>
-    <row r="101" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4289,7 +4289,7 @@
       <c r="BD101" s="4"/>
       <c r="BE101" s="4"/>
     </row>
-    <row r="102" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4313,7 +4313,7 @@
       <c r="BD102" s="4"/>
       <c r="BE102" s="4"/>
     </row>
-    <row r="103" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4337,7 +4337,7 @@
       <c r="BD103" s="4"/>
       <c r="BE103" s="4"/>
     </row>
-    <row r="104" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4361,7 +4361,7 @@
       <c r="BD104" s="4"/>
       <c r="BE104" s="4"/>
     </row>
-    <row r="105" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4385,7 +4385,7 @@
       <c r="BD105" s="4"/>
       <c r="BE105" s="4"/>
     </row>
-    <row r="106" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4409,7 +4409,7 @@
       <c r="BD106" s="4"/>
       <c r="BE106" s="4"/>
     </row>
-    <row r="107" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4433,7 +4433,7 @@
       <c r="BD107" s="4"/>
       <c r="BE107" s="4"/>
     </row>
-    <row r="108" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4457,7 +4457,7 @@
       <c r="BD108" s="4"/>
       <c r="BE108" s="4"/>
     </row>
-    <row r="109" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4481,7 +4481,7 @@
       <c r="BD109" s="4"/>
       <c r="BE109" s="4"/>
     </row>
-    <row r="110" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4505,7 +4505,7 @@
       <c r="BD110" s="4"/>
       <c r="BE110" s="4"/>
     </row>
-    <row r="111" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4529,7 +4529,7 @@
       <c r="BD111" s="4"/>
       <c r="BE111" s="4"/>
     </row>
-    <row r="112" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4553,7 +4553,7 @@
       <c r="BD112" s="4"/>
       <c r="BE112" s="4"/>
     </row>
-    <row r="113" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4577,7 +4577,7 @@
       <c r="BD113" s="4"/>
       <c r="BE113" s="4"/>
     </row>
-    <row r="114" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4601,7 +4601,7 @@
       <c r="BD114" s="4"/>
       <c r="BE114" s="4"/>
     </row>
-    <row r="115" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4625,7 +4625,7 @@
       <c r="BD115" s="4"/>
       <c r="BE115" s="4"/>
     </row>
-    <row r="116" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4649,7 +4649,7 @@
       <c r="BD116" s="4"/>
       <c r="BE116" s="4"/>
     </row>
-    <row r="117" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4673,7 +4673,7 @@
       <c r="BD117" s="4"/>
       <c r="BE117" s="4"/>
     </row>
-    <row r="118" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4697,7 +4697,7 @@
       <c r="BD118" s="4"/>
       <c r="BE118" s="4"/>
     </row>
-    <row r="119" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4721,7 +4721,7 @@
       <c r="BD119" s="4"/>
       <c r="BE119" s="4"/>
     </row>
-    <row r="120" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4745,7 +4745,7 @@
       <c r="BD120" s="4"/>
       <c r="BE120" s="4"/>
     </row>
-    <row r="121" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4769,7 +4769,7 @@
       <c r="BD121" s="4"/>
       <c r="BE121" s="4"/>
     </row>
-    <row r="122" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4793,7 +4793,7 @@
       <c r="BD122" s="4"/>
       <c r="BE122" s="4"/>
     </row>
-    <row r="123" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4817,7 +4817,7 @@
       <c r="BD123" s="4"/>
       <c r="BE123" s="4"/>
     </row>
-    <row r="124" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4841,7 +4841,7 @@
       <c r="BD124" s="4"/>
       <c r="BE124" s="4"/>
     </row>
-    <row r="125" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4865,7 +4865,7 @@
       <c r="BD125" s="4"/>
       <c r="BE125" s="4"/>
     </row>
-    <row r="126" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4889,7 +4889,7 @@
       <c r="BD126" s="4"/>
       <c r="BE126" s="4"/>
     </row>
-    <row r="127" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4913,7 +4913,7 @@
       <c r="BD127" s="4"/>
       <c r="BE127" s="4"/>
     </row>
-    <row r="128" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4937,7 +4937,7 @@
       <c r="BD128" s="4"/>
       <c r="BE128" s="4"/>
     </row>
-    <row r="129" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4961,7 +4961,7 @@
       <c r="BD129" s="4"/>
       <c r="BE129" s="4"/>
     </row>
-    <row r="130" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4985,7 +4985,7 @@
       <c r="BD130" s="4"/>
       <c r="BE130" s="4"/>
     </row>
-    <row r="131" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -5009,7 +5009,7 @@
       <c r="BD131" s="4"/>
       <c r="BE131" s="4"/>
     </row>
-    <row r="132" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -5033,7 +5033,7 @@
       <c r="BD132" s="4"/>
       <c r="BE132" s="4"/>
     </row>
-    <row r="133" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -5057,7 +5057,7 @@
       <c r="BD133" s="4"/>
       <c r="BE133" s="4"/>
     </row>
-    <row r="134" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -5081,7 +5081,7 @@
       <c r="BD134" s="4"/>
       <c r="BE134" s="4"/>
     </row>
-    <row r="135" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -5105,7 +5105,7 @@
       <c r="BD135" s="4"/>
       <c r="BE135" s="4"/>
     </row>
-    <row r="136" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -5129,7 +5129,7 @@
       <c r="BD136" s="4"/>
       <c r="BE136" s="4"/>
     </row>
-    <row r="137" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -5153,7 +5153,7 @@
       <c r="BD137" s="4"/>
       <c r="BE137" s="4"/>
     </row>
-    <row r="138" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -5177,7 +5177,7 @@
       <c r="BD138" s="4"/>
       <c r="BE138" s="4"/>
     </row>
-    <row r="139" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -5201,7 +5201,7 @@
       <c r="BD139" s="4"/>
       <c r="BE139" s="4"/>
     </row>
-    <row r="140" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -5225,7 +5225,7 @@
       <c r="BD140" s="4"/>
       <c r="BE140" s="4"/>
     </row>
-    <row r="141" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -5249,7 +5249,7 @@
       <c r="BD141" s="4"/>
       <c r="BE141" s="4"/>
     </row>
-    <row r="142" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -5273,7 +5273,7 @@
       <c r="BD142" s="4"/>
       <c r="BE142" s="4"/>
     </row>
-    <row r="143" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -5297,7 +5297,7 @@
       <c r="BD143" s="4"/>
       <c r="BE143" s="4"/>
     </row>
-    <row r="144" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -5321,7 +5321,7 @@
       <c r="BD144" s="4"/>
       <c r="BE144" s="4"/>
     </row>
-    <row r="145" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -5345,7 +5345,7 @@
       <c r="BD145" s="4"/>
       <c r="BE145" s="4"/>
     </row>
-    <row r="146" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -5369,7 +5369,7 @@
       <c r="BD146" s="4"/>
       <c r="BE146" s="4"/>
     </row>
-    <row r="147" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -5393,7 +5393,7 @@
       <c r="BD147" s="4"/>
       <c r="BE147" s="4"/>
     </row>
-    <row r="148" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -5417,7 +5417,7 @@
       <c r="BD148" s="4"/>
       <c r="BE148" s="4"/>
     </row>
-    <row r="149" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -5441,7 +5441,7 @@
       <c r="BD149" s="4"/>
       <c r="BE149" s="4"/>
     </row>
-    <row r="150" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -5465,7 +5465,7 @@
       <c r="BD150" s="4"/>
       <c r="BE150" s="4"/>
     </row>
-    <row r="151" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -5489,7 +5489,7 @@
       <c r="BD151" s="4"/>
       <c r="BE151" s="4"/>
     </row>
-    <row r="152" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -5513,7 +5513,7 @@
       <c r="BD152" s="4"/>
       <c r="BE152" s="4"/>
     </row>
-    <row r="153" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -5537,7 +5537,7 @@
       <c r="BD153" s="4"/>
       <c r="BE153" s="4"/>
     </row>
-    <row r="154" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -5561,7 +5561,7 @@
       <c r="BD154" s="4"/>
       <c r="BE154" s="4"/>
     </row>
-    <row r="155" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -5585,7 +5585,7 @@
       <c r="BD155" s="4"/>
       <c r="BE155" s="4"/>
     </row>
-    <row r="156" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -5609,7 +5609,7 @@
       <c r="BD156" s="4"/>
       <c r="BE156" s="4"/>
     </row>
-    <row r="157" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5633,7 +5633,7 @@
       <c r="BD157" s="4"/>
       <c r="BE157" s="4"/>
     </row>
-    <row r="158" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -5657,7 +5657,7 @@
       <c r="BD158" s="4"/>
       <c r="BE158" s="4"/>
     </row>
-    <row r="159" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -5681,7 +5681,7 @@
       <c r="BD159" s="4"/>
       <c r="BE159" s="4"/>
     </row>
-    <row r="160" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -5705,7 +5705,7 @@
       <c r="BD160" s="4"/>
       <c r="BE160" s="4"/>
     </row>
-    <row r="161" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -5729,7 +5729,7 @@
       <c r="BD161" s="4"/>
       <c r="BE161" s="4"/>
     </row>
-    <row r="162" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5753,7 +5753,7 @@
       <c r="BD162" s="4"/>
       <c r="BE162" s="4"/>
     </row>
-    <row r="163" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -5777,7 +5777,7 @@
       <c r="BD163" s="4"/>
       <c r="BE163" s="4"/>
     </row>
-    <row r="164" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -5801,7 +5801,7 @@
       <c r="BD164" s="4"/>
       <c r="BE164" s="4"/>
     </row>
-    <row r="165" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5825,7 +5825,7 @@
       <c r="BD165" s="4"/>
       <c r="BE165" s="4"/>
     </row>
-    <row r="166" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -5849,7 +5849,7 @@
       <c r="BD166" s="4"/>
       <c r="BE166" s="4"/>
     </row>
-    <row r="167" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5873,7 +5873,7 @@
       <c r="BD167" s="4"/>
       <c r="BE167" s="4"/>
     </row>
-    <row r="168" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5897,7 +5897,7 @@
       <c r="BD168" s="4"/>
       <c r="BE168" s="4"/>
     </row>
-    <row r="169" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5921,7 +5921,7 @@
       <c r="BD169" s="4"/>
       <c r="BE169" s="4"/>
     </row>
-    <row r="170" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5945,7 +5945,7 @@
       <c r="BD170" s="4"/>
       <c r="BE170" s="4"/>
     </row>
-    <row r="171" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5969,7 +5969,7 @@
       <c r="BD171" s="4"/>
       <c r="BE171" s="4"/>
     </row>
-    <row r="172" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5993,7 +5993,7 @@
       <c r="BD172" s="4"/>
       <c r="BE172" s="4"/>
     </row>
-    <row r="173" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6017,7 +6017,7 @@
       <c r="BD173" s="4"/>
       <c r="BE173" s="4"/>
     </row>
-    <row r="174" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6041,7 +6041,7 @@
       <c r="BD174" s="4"/>
       <c r="BE174" s="4"/>
     </row>
-    <row r="175" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6065,7 +6065,7 @@
       <c r="BD175" s="4"/>
       <c r="BE175" s="4"/>
     </row>
-    <row r="176" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6089,7 +6089,7 @@
       <c r="BD176" s="4"/>
       <c r="BE176" s="4"/>
     </row>
-    <row r="177" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -6113,7 +6113,7 @@
       <c r="BD177" s="4"/>
       <c r="BE177" s="4"/>
     </row>
-    <row r="178" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -6137,7 +6137,7 @@
       <c r="BD178" s="4"/>
       <c r="BE178" s="4"/>
     </row>
-    <row r="179" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -6161,7 +6161,7 @@
       <c r="BD179" s="4"/>
       <c r="BE179" s="4"/>
     </row>
-    <row r="180" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -6185,7 +6185,7 @@
       <c r="BD180" s="4"/>
       <c r="BE180" s="4"/>
     </row>
-    <row r="181" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -6209,7 +6209,7 @@
       <c r="BD181" s="4"/>
       <c r="BE181" s="4"/>
     </row>
-    <row r="182" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -6233,7 +6233,7 @@
       <c r="BD182" s="4"/>
       <c r="BE182" s="4"/>
     </row>
-    <row r="183" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -6257,7 +6257,7 @@
       <c r="BD183" s="4"/>
       <c r="BE183" s="4"/>
     </row>
-    <row r="184" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -6281,7 +6281,7 @@
       <c r="BD184" s="4"/>
       <c r="BE184" s="4"/>
     </row>
-    <row r="185" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -6305,7 +6305,7 @@
       <c r="BD185" s="4"/>
       <c r="BE185" s="4"/>
     </row>
-    <row r="186" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -6329,7 +6329,7 @@
       <c r="BD186" s="4"/>
       <c r="BE186" s="4"/>
     </row>
-    <row r="187" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -6353,7 +6353,7 @@
       <c r="BD187" s="4"/>
       <c r="BE187" s="4"/>
     </row>
-    <row r="188" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -6377,7 +6377,7 @@
       <c r="BD188" s="4"/>
       <c r="BE188" s="4"/>
     </row>
-    <row r="189" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -6401,7 +6401,7 @@
       <c r="BD189" s="4"/>
       <c r="BE189" s="4"/>
     </row>
-    <row r="190" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -6425,7 +6425,7 @@
       <c r="BD190" s="4"/>
       <c r="BE190" s="4"/>
     </row>
-    <row r="191" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -6449,7 +6449,7 @@
       <c r="BD191" s="4"/>
       <c r="BE191" s="4"/>
     </row>
-    <row r="192" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -6473,7 +6473,7 @@
       <c r="BD192" s="4"/>
       <c r="BE192" s="4"/>
     </row>
-    <row r="193" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -6497,7 +6497,7 @@
       <c r="BD193" s="4"/>
       <c r="BE193" s="4"/>
     </row>
-    <row r="194" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -6521,7 +6521,7 @@
       <c r="BD194" s="4"/>
       <c r="BE194" s="4"/>
     </row>
-    <row r="195" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -6545,7 +6545,7 @@
       <c r="BD195" s="4"/>
       <c r="BE195" s="4"/>
     </row>
-    <row r="196" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -6569,7 +6569,7 @@
       <c r="BD196" s="4"/>
       <c r="BE196" s="4"/>
     </row>
-    <row r="197" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -6593,7 +6593,7 @@
       <c r="BD197" s="4"/>
       <c r="BE197" s="4"/>
     </row>
-    <row r="198" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -6617,7 +6617,7 @@
       <c r="BD198" s="4"/>
       <c r="BE198" s="4"/>
     </row>
-    <row r="199" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -6641,7 +6641,7 @@
       <c r="BD199" s="4"/>
       <c r="BE199" s="4"/>
     </row>
-    <row r="200" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -6665,7 +6665,7 @@
       <c r="BD200" s="4"/>
       <c r="BE200" s="4"/>
     </row>
-    <row r="201" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -6689,7 +6689,7 @@
       <c r="BD201" s="4"/>
       <c r="BE201" s="4"/>
     </row>
-    <row r="202" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -6713,7 +6713,7 @@
       <c r="BD202" s="4"/>
       <c r="BE202" s="4"/>
     </row>
-    <row r="203" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -6737,7 +6737,7 @@
       <c r="BD203" s="4"/>
       <c r="BE203" s="4"/>
     </row>
-    <row r="204" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -6761,7 +6761,7 @@
       <c r="BD204" s="4"/>
       <c r="BE204" s="4"/>
     </row>
-    <row r="205" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -6785,7 +6785,7 @@
       <c r="BD205" s="4"/>
       <c r="BE205" s="4"/>
     </row>
-    <row r="206" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -6809,7 +6809,7 @@
       <c r="BD206" s="4"/>
       <c r="BE206" s="4"/>
     </row>
-    <row r="207" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -6833,7 +6833,7 @@
       <c r="BD207" s="4"/>
       <c r="BE207" s="4"/>
     </row>
-    <row r="208" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -6857,7 +6857,7 @@
       <c r="BD208" s="4"/>
       <c r="BE208" s="4"/>
     </row>
-    <row r="209" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -6881,7 +6881,7 @@
       <c r="BD209" s="4"/>
       <c r="BE209" s="4"/>
     </row>
-    <row r="210" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -6905,7 +6905,7 @@
       <c r="BD210" s="4"/>
       <c r="BE210" s="4"/>
     </row>
-    <row r="211" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -6929,7 +6929,7 @@
       <c r="BD211" s="4"/>
       <c r="BE211" s="4"/>
     </row>
-    <row r="212" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -6953,7 +6953,7 @@
       <c r="BD212" s="4"/>
       <c r="BE212" s="4"/>
     </row>
-    <row r="213" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -6977,7 +6977,7 @@
       <c r="BD213" s="4"/>
       <c r="BE213" s="4"/>
     </row>
-    <row r="214" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -7001,7 +7001,7 @@
       <c r="BD214" s="4"/>
       <c r="BE214" s="4"/>
     </row>
-    <row r="215" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -7025,7 +7025,7 @@
       <c r="BD215" s="4"/>
       <c r="BE215" s="4"/>
     </row>
-    <row r="216" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -7049,7 +7049,7 @@
       <c r="BD216" s="4"/>
       <c r="BE216" s="4"/>
     </row>
-    <row r="217" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -7073,7 +7073,7 @@
       <c r="BD217" s="4"/>
       <c r="BE217" s="4"/>
     </row>
-    <row r="218" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -7097,7 +7097,7 @@
       <c r="BD218" s="4"/>
       <c r="BE218" s="4"/>
     </row>
-    <row r="219" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -7121,7 +7121,7 @@
       <c r="BD219" s="4"/>
       <c r="BE219" s="4"/>
     </row>
-    <row r="220" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -7145,7 +7145,7 @@
       <c r="BD220" s="4"/>
       <c r="BE220" s="4"/>
     </row>
-    <row r="221" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -7169,7 +7169,7 @@
       <c r="BD221" s="4"/>
       <c r="BE221" s="4"/>
     </row>
-    <row r="222" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -7193,7 +7193,7 @@
       <c r="BD222" s="4"/>
       <c r="BE222" s="4"/>
     </row>
-    <row r="223" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -7217,7 +7217,7 @@
       <c r="BD223" s="4"/>
       <c r="BE223" s="4"/>
     </row>
-    <row r="224" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -7241,7 +7241,7 @@
       <c r="BD224" s="4"/>
       <c r="BE224" s="4"/>
     </row>
-    <row r="225" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -7265,7 +7265,7 @@
       <c r="BD225" s="4"/>
       <c r="BE225" s="4"/>
     </row>
-    <row r="226" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -7289,7 +7289,7 @@
       <c r="BD226" s="4"/>
       <c r="BE226" s="4"/>
     </row>
-    <row r="227" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -7313,7 +7313,7 @@
       <c r="BD227" s="4"/>
       <c r="BE227" s="4"/>
     </row>
-    <row r="228" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -7337,7 +7337,7 @@
       <c r="BD228" s="4"/>
       <c r="BE228" s="4"/>
     </row>
-    <row r="229" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -7361,7 +7361,7 @@
       <c r="BD229" s="4"/>
       <c r="BE229" s="4"/>
     </row>
-    <row r="230" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -7385,7 +7385,7 @@
       <c r="BD230" s="4"/>
       <c r="BE230" s="4"/>
     </row>
-    <row r="231" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -7409,7 +7409,7 @@
       <c r="BD231" s="4"/>
       <c r="BE231" s="4"/>
     </row>
-    <row r="232" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -7433,7 +7433,7 @@
       <c r="BD232" s="4"/>
       <c r="BE232" s="4"/>
     </row>
-    <row r="233" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -7457,7 +7457,7 @@
       <c r="BD233" s="4"/>
       <c r="BE233" s="4"/>
     </row>
-    <row r="234" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -7481,7 +7481,7 @@
       <c r="BD234" s="4"/>
       <c r="BE234" s="4"/>
     </row>
-    <row r="235" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -7505,7 +7505,7 @@
       <c r="BD235" s="4"/>
       <c r="BE235" s="4"/>
     </row>
-    <row r="236" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -7529,7 +7529,7 @@
       <c r="BD236" s="4"/>
       <c r="BE236" s="4"/>
     </row>
-    <row r="237" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -7553,7 +7553,7 @@
       <c r="BD237" s="4"/>
       <c r="BE237" s="4"/>
     </row>
-    <row r="238" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -7577,7 +7577,7 @@
       <c r="BD238" s="4"/>
       <c r="BE238" s="4"/>
     </row>
-    <row r="239" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -7601,7 +7601,7 @@
       <c r="BD239" s="4"/>
       <c r="BE239" s="4"/>
     </row>
-    <row r="240" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -7625,7 +7625,7 @@
       <c r="BD240" s="4"/>
       <c r="BE240" s="4"/>
     </row>
-    <row r="241" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -7649,7 +7649,7 @@
       <c r="BD241" s="4"/>
       <c r="BE241" s="4"/>
     </row>
-    <row r="242" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -7673,7 +7673,7 @@
       <c r="BD242" s="4"/>
       <c r="BE242" s="4"/>
     </row>
-    <row r="243" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -7697,7 +7697,7 @@
       <c r="BD243" s="4"/>
       <c r="BE243" s="4"/>
     </row>
-    <row r="244" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -7721,7 +7721,7 @@
       <c r="BD244" s="4"/>
       <c r="BE244" s="4"/>
     </row>
-    <row r="245" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -7745,7 +7745,7 @@
       <c r="BD245" s="4"/>
       <c r="BE245" s="4"/>
     </row>
-    <row r="246" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -7769,7 +7769,7 @@
       <c r="BD246" s="4"/>
       <c r="BE246" s="4"/>
     </row>
-    <row r="247" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -7793,7 +7793,7 @@
       <c r="BD247" s="4"/>
       <c r="BE247" s="4"/>
     </row>
-    <row r="248" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -7817,7 +7817,7 @@
       <c r="BD248" s="4"/>
       <c r="BE248" s="4"/>
     </row>
-    <row r="249" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -7841,7 +7841,7 @@
       <c r="BD249" s="4"/>
       <c r="BE249" s="4"/>
     </row>
-    <row r="250" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -7865,7 +7865,7 @@
       <c r="BD250" s="4"/>
       <c r="BE250" s="4"/>
     </row>
-    <row r="251" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -7889,7 +7889,7 @@
       <c r="BD251" s="4"/>
       <c r="BE251" s="4"/>
     </row>
-    <row r="252" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -7913,7 +7913,7 @@
       <c r="BD252" s="4"/>
       <c r="BE252" s="4"/>
     </row>
-    <row r="253" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -7937,7 +7937,7 @@
       <c r="BD253" s="4"/>
       <c r="BE253" s="4"/>
     </row>
-    <row r="254" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -7961,7 +7961,7 @@
       <c r="BD254" s="4"/>
       <c r="BE254" s="4"/>
     </row>
-    <row r="255" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -7985,7 +7985,7 @@
       <c r="BD255" s="4"/>
       <c r="BE255" s="4"/>
     </row>
-    <row r="256" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -8009,7 +8009,7 @@
       <c r="BD256" s="4"/>
       <c r="BE256" s="4"/>
     </row>
-    <row r="257" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -8033,7 +8033,7 @@
       <c r="BD257" s="4"/>
       <c r="BE257" s="4"/>
     </row>
-    <row r="258" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -8057,7 +8057,7 @@
       <c r="BD258" s="4"/>
       <c r="BE258" s="4"/>
     </row>
-    <row r="259" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -8081,7 +8081,7 @@
       <c r="BD259" s="4"/>
       <c r="BE259" s="4"/>
     </row>
-    <row r="260" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -8105,7 +8105,7 @@
       <c r="BD260" s="4"/>
       <c r="BE260" s="4"/>
     </row>
-    <row r="261" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -8129,7 +8129,7 @@
       <c r="BD261" s="4"/>
       <c r="BE261" s="4"/>
     </row>
-    <row r="262" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -8153,7 +8153,7 @@
       <c r="BD262" s="4"/>
       <c r="BE262" s="4"/>
     </row>
-    <row r="263" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -8177,7 +8177,7 @@
       <c r="BD263" s="4"/>
       <c r="BE263" s="4"/>
     </row>
-    <row r="264" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -8201,7 +8201,7 @@
       <c r="BD264" s="4"/>
       <c r="BE264" s="4"/>
     </row>
-    <row r="265" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -8225,7 +8225,7 @@
       <c r="BD265" s="4"/>
       <c r="BE265" s="4"/>
     </row>
-    <row r="266" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -8249,7 +8249,7 @@
       <c r="BD266" s="4"/>
       <c r="BE266" s="4"/>
     </row>
-    <row r="267" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -8273,7 +8273,7 @@
       <c r="BD267" s="4"/>
       <c r="BE267" s="4"/>
     </row>
-    <row r="268" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -8297,7 +8297,7 @@
       <c r="BD268" s="4"/>
       <c r="BE268" s="4"/>
     </row>
-    <row r="269" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -8321,7 +8321,7 @@
       <c r="BD269" s="4"/>
       <c r="BE269" s="4"/>
     </row>
-    <row r="270" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -8345,7 +8345,7 @@
       <c r="BD270" s="4"/>
       <c r="BE270" s="4"/>
     </row>
-    <row r="271" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -8369,7 +8369,7 @@
       <c r="BD271" s="4"/>
       <c r="BE271" s="4"/>
     </row>
-    <row r="272" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -8393,7 +8393,7 @@
       <c r="BD272" s="4"/>
       <c r="BE272" s="4"/>
     </row>
-    <row r="273" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -8417,7 +8417,7 @@
       <c r="BD273" s="4"/>
       <c r="BE273" s="4"/>
     </row>
-    <row r="274" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -8441,7 +8441,7 @@
       <c r="BD274" s="4"/>
       <c r="BE274" s="4"/>
     </row>
-    <row r="275" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -8465,7 +8465,7 @@
       <c r="BD275" s="4"/>
       <c r="BE275" s="4"/>
     </row>
-    <row r="276" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -8489,7 +8489,7 @@
       <c r="BD276" s="4"/>
       <c r="BE276" s="4"/>
     </row>
-    <row r="277" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -8513,7 +8513,7 @@
       <c r="BD277" s="4"/>
       <c r="BE277" s="4"/>
     </row>
-    <row r="278" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -8537,7 +8537,7 @@
       <c r="BD278" s="4"/>
       <c r="BE278" s="4"/>
     </row>
-    <row r="279" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -8561,7 +8561,7 @@
       <c r="BD279" s="4"/>
       <c r="BE279" s="4"/>
     </row>
-    <row r="280" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -8585,7 +8585,7 @@
       <c r="BD280" s="4"/>
       <c r="BE280" s="4"/>
     </row>
-    <row r="281" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -8609,7 +8609,7 @@
       <c r="BD281" s="4"/>
       <c r="BE281" s="4"/>
     </row>
-    <row r="282" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -8633,7 +8633,7 @@
       <c r="BD282" s="4"/>
       <c r="BE282" s="4"/>
     </row>
-    <row r="283" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -8657,7 +8657,7 @@
       <c r="BD283" s="4"/>
       <c r="BE283" s="4"/>
     </row>
-    <row r="284" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -8681,7 +8681,7 @@
       <c r="BD284" s="4"/>
       <c r="BE284" s="4"/>
     </row>
-    <row r="285" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -8705,7 +8705,7 @@
       <c r="BD285" s="4"/>
       <c r="BE285" s="4"/>
     </row>
-    <row r="286" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -8729,7 +8729,7 @@
       <c r="BD286" s="4"/>
       <c r="BE286" s="4"/>
     </row>
-    <row r="287" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -8753,7 +8753,7 @@
       <c r="BD287" s="4"/>
       <c r="BE287" s="4"/>
     </row>
-    <row r="288" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -8777,7 +8777,7 @@
       <c r="BD288" s="4"/>
       <c r="BE288" s="4"/>
     </row>
-    <row r="289" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -8801,7 +8801,7 @@
       <c r="BD289" s="4"/>
       <c r="BE289" s="4"/>
     </row>
-    <row r="290" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -8825,7 +8825,7 @@
       <c r="BD290" s="4"/>
       <c r="BE290" s="4"/>
     </row>
-    <row r="291" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -8849,7 +8849,7 @@
       <c r="BD291" s="4"/>
       <c r="BE291" s="4"/>
     </row>
-    <row r="292" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -8873,7 +8873,7 @@
       <c r="BD292" s="4"/>
       <c r="BE292" s="4"/>
     </row>
-    <row r="293" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -8897,7 +8897,7 @@
       <c r="BD293" s="4"/>
       <c r="BE293" s="4"/>
     </row>
-    <row r="294" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -8921,7 +8921,7 @@
       <c r="BD294" s="4"/>
       <c r="BE294" s="4"/>
     </row>
-    <row r="295" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -8945,7 +8945,7 @@
       <c r="BD295" s="4"/>
       <c r="BE295" s="4"/>
     </row>
-    <row r="296" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -8969,7 +8969,7 @@
       <c r="BD296" s="4"/>
       <c r="BE296" s="4"/>
     </row>
-    <row r="297" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -8993,7 +8993,7 @@
       <c r="BD297" s="4"/>
       <c r="BE297" s="4"/>
     </row>
-    <row r="298" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -9017,7 +9017,7 @@
       <c r="BD298" s="4"/>
       <c r="BE298" s="4"/>
     </row>
-    <row r="299" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -9041,7 +9041,7 @@
       <c r="BD299" s="4"/>
       <c r="BE299" s="4"/>
     </row>
-    <row r="300" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -9065,7 +9065,7 @@
       <c r="BD300" s="4"/>
       <c r="BE300" s="4"/>
     </row>
-    <row r="301" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -9089,7 +9089,7 @@
       <c r="BD301" s="4"/>
       <c r="BE301" s="4"/>
     </row>
-    <row r="302" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -9113,7 +9113,7 @@
       <c r="BD302" s="4"/>
       <c r="BE302" s="4"/>
     </row>
-    <row r="303" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -9137,7 +9137,7 @@
       <c r="BD303" s="4"/>
       <c r="BE303" s="4"/>
     </row>
-    <row r="304" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -9161,7 +9161,7 @@
       <c r="BD304" s="4"/>
       <c r="BE304" s="4"/>
     </row>
-    <row r="305" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -9185,7 +9185,7 @@
       <c r="BD305" s="4"/>
       <c r="BE305" s="4"/>
     </row>
-    <row r="306" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -9209,7 +9209,7 @@
       <c r="BD306" s="4"/>
       <c r="BE306" s="4"/>
     </row>
-    <row r="307" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -9233,7 +9233,7 @@
       <c r="BD307" s="4"/>
       <c r="BE307" s="4"/>
     </row>
-    <row r="308" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -9257,7 +9257,7 @@
       <c r="BD308" s="4"/>
       <c r="BE308" s="4"/>
     </row>
-    <row r="309" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -9281,7 +9281,7 @@
       <c r="BD309" s="4"/>
       <c r="BE309" s="4"/>
     </row>
-    <row r="310" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -9305,7 +9305,7 @@
       <c r="BD310" s="4"/>
       <c r="BE310" s="4"/>
     </row>
-    <row r="311" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -9329,7 +9329,7 @@
       <c r="BD311" s="4"/>
       <c r="BE311" s="4"/>
     </row>
-    <row r="312" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -9353,7 +9353,7 @@
       <c r="BD312" s="4"/>
       <c r="BE312" s="4"/>
     </row>
-    <row r="313" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -9377,7 +9377,7 @@
       <c r="BD313" s="4"/>
       <c r="BE313" s="4"/>
     </row>
-    <row r="314" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -9401,7 +9401,7 @@
       <c r="BD314" s="4"/>
       <c r="BE314" s="4"/>
     </row>
-    <row r="315" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -9425,7 +9425,7 @@
       <c r="BD315" s="4"/>
       <c r="BE315" s="4"/>
     </row>
-    <row r="316" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -9449,7 +9449,7 @@
       <c r="BD316" s="4"/>
       <c r="BE316" s="4"/>
     </row>
-    <row r="317" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -9473,7 +9473,7 @@
       <c r="BD317" s="4"/>
       <c r="BE317" s="4"/>
     </row>
-    <row r="318" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -9497,7 +9497,7 @@
       <c r="BD318" s="4"/>
       <c r="BE318" s="4"/>
     </row>
-    <row r="319" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -9521,7 +9521,7 @@
       <c r="BD319" s="4"/>
       <c r="BE319" s="4"/>
     </row>
-    <row r="320" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -9545,7 +9545,7 @@
       <c r="BD320" s="4"/>
       <c r="BE320" s="4"/>
     </row>
-    <row r="321" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -9569,7 +9569,7 @@
       <c r="BD321" s="4"/>
       <c r="BE321" s="4"/>
     </row>
-    <row r="322" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -9593,7 +9593,7 @@
       <c r="BD322" s="4"/>
       <c r="BE322" s="4"/>
     </row>
-    <row r="323" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -9617,7 +9617,7 @@
       <c r="BD323" s="4"/>
       <c r="BE323" s="4"/>
     </row>
-    <row r="324" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -9641,7 +9641,7 @@
       <c r="BD324" s="4"/>
       <c r="BE324" s="4"/>
     </row>
-    <row r="325" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -9665,7 +9665,7 @@
       <c r="BD325" s="4"/>
       <c r="BE325" s="4"/>
     </row>
-    <row r="326" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -9689,7 +9689,7 @@
       <c r="BD326" s="4"/>
       <c r="BE326" s="4"/>
     </row>
-    <row r="327" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -9713,7 +9713,7 @@
       <c r="BD327" s="4"/>
       <c r="BE327" s="4"/>
     </row>
-    <row r="328" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -9737,7 +9737,7 @@
       <c r="BD328" s="4"/>
       <c r="BE328" s="4"/>
     </row>
-    <row r="329" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -9761,7 +9761,7 @@
       <c r="BD329" s="4"/>
       <c r="BE329" s="4"/>
     </row>
-    <row r="330" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -9785,7 +9785,7 @@
       <c r="BD330" s="4"/>
       <c r="BE330" s="4"/>
     </row>
-    <row r="331" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -9809,7 +9809,7 @@
       <c r="BD331" s="4"/>
       <c r="BE331" s="4"/>
     </row>
-    <row r="332" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -9833,7 +9833,7 @@
       <c r="BD332" s="4"/>
       <c r="BE332" s="4"/>
     </row>
-    <row r="333" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -9857,7 +9857,7 @@
       <c r="BD333" s="4"/>
       <c r="BE333" s="4"/>
     </row>
-    <row r="334" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -9881,7 +9881,7 @@
       <c r="BD334" s="4"/>
       <c r="BE334" s="4"/>
     </row>
-    <row r="335" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -9905,7 +9905,7 @@
       <c r="BD335" s="4"/>
       <c r="BE335" s="4"/>
     </row>
-    <row r="336" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -9929,7 +9929,7 @@
       <c r="BD336" s="4"/>
       <c r="BE336" s="4"/>
     </row>
-    <row r="337" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -9953,7 +9953,7 @@
       <c r="BD337" s="4"/>
       <c r="BE337" s="4"/>
     </row>
-    <row r="338" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -9977,7 +9977,7 @@
       <c r="BD338" s="4"/>
       <c r="BE338" s="4"/>
     </row>
-    <row r="339" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -10001,7 +10001,7 @@
       <c r="BD339" s="4"/>
       <c r="BE339" s="4"/>
     </row>
-    <row r="340" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -10025,7 +10025,7 @@
       <c r="BD340" s="4"/>
       <c r="BE340" s="4"/>
     </row>
-    <row r="341" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -10049,7 +10049,7 @@
       <c r="BD341" s="4"/>
       <c r="BE341" s="4"/>
     </row>
-    <row r="342" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -10073,7 +10073,7 @@
       <c r="BD342" s="4"/>
       <c r="BE342" s="4"/>
     </row>
-    <row r="343" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -10097,7 +10097,7 @@
       <c r="BD343" s="4"/>
       <c r="BE343" s="4"/>
     </row>
-    <row r="344" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -10121,7 +10121,7 @@
       <c r="BD344" s="4"/>
       <c r="BE344" s="4"/>
     </row>
-    <row r="345" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -10145,7 +10145,7 @@
       <c r="BD345" s="4"/>
       <c r="BE345" s="4"/>
     </row>
-    <row r="346" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -10169,7 +10169,7 @@
       <c r="BD346" s="4"/>
       <c r="BE346" s="4"/>
     </row>
-    <row r="347" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -10193,7 +10193,7 @@
       <c r="BD347" s="4"/>
       <c r="BE347" s="4"/>
     </row>
-    <row r="348" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -10217,7 +10217,7 @@
       <c r="BD348" s="4"/>
       <c r="BE348" s="4"/>
     </row>
-    <row r="349" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -10241,7 +10241,7 @@
       <c r="BD349" s="4"/>
       <c r="BE349" s="4"/>
     </row>
-    <row r="350" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -10265,7 +10265,7 @@
       <c r="BD350" s="4"/>
       <c r="BE350" s="4"/>
     </row>
-    <row r="351" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -10289,7 +10289,7 @@
       <c r="BD351" s="4"/>
       <c r="BE351" s="4"/>
     </row>
-    <row r="352" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -10313,7 +10313,7 @@
       <c r="BD352" s="4"/>
       <c r="BE352" s="4"/>
     </row>
-    <row r="353" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -10337,7 +10337,7 @@
       <c r="BD353" s="4"/>
       <c r="BE353" s="4"/>
     </row>
-    <row r="354" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -10361,7 +10361,7 @@
       <c r="BD354" s="4"/>
       <c r="BE354" s="4"/>
     </row>
-    <row r="355" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -10385,7 +10385,7 @@
       <c r="BD355" s="4"/>
       <c r="BE355" s="4"/>
     </row>
-    <row r="356" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -10409,7 +10409,7 @@
       <c r="BD356" s="4"/>
       <c r="BE356" s="4"/>
     </row>
-    <row r="357" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -10433,7 +10433,7 @@
       <c r="BD357" s="4"/>
       <c r="BE357" s="4"/>
     </row>
-    <row r="358" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -10457,7 +10457,7 @@
       <c r="BD358" s="4"/>
       <c r="BE358" s="4"/>
     </row>
-    <row r="359" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -10481,7 +10481,7 @@
       <c r="BD359" s="4"/>
       <c r="BE359" s="4"/>
     </row>
-    <row r="360" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -10505,7 +10505,7 @@
       <c r="BD360" s="4"/>
       <c r="BE360" s="4"/>
     </row>
-    <row r="361" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -10529,7 +10529,7 @@
       <c r="BD361" s="4"/>
       <c r="BE361" s="4"/>
     </row>
-    <row r="362" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -10553,7 +10553,7 @@
       <c r="BD362" s="4"/>
       <c r="BE362" s="4"/>
     </row>
-    <row r="363" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -10577,7 +10577,7 @@
       <c r="BD363" s="4"/>
       <c r="BE363" s="4"/>
     </row>
-    <row r="364" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -10601,7 +10601,7 @@
       <c r="BD364" s="4"/>
       <c r="BE364" s="4"/>
     </row>
-    <row r="365" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -10625,7 +10625,7 @@
       <c r="BD365" s="4"/>
       <c r="BE365" s="4"/>
     </row>
-    <row r="366" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -10649,7 +10649,7 @@
       <c r="BD366" s="4"/>
       <c r="BE366" s="4"/>
     </row>
-    <row r="367" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -10673,7 +10673,7 @@
       <c r="BD367" s="4"/>
       <c r="BE367" s="4"/>
     </row>
-    <row r="368" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -10697,7 +10697,7 @@
       <c r="BD368" s="4"/>
       <c r="BE368" s="4"/>
     </row>
-    <row r="369" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -10721,7 +10721,7 @@
       <c r="BD369" s="4"/>
       <c r="BE369" s="4"/>
     </row>
-    <row r="370" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -10745,7 +10745,7 @@
       <c r="BD370" s="4"/>
       <c r="BE370" s="4"/>
     </row>
-    <row r="371" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -10769,7 +10769,7 @@
       <c r="BD371" s="4"/>
       <c r="BE371" s="4"/>
     </row>
-    <row r="372" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -10793,7 +10793,7 @@
       <c r="BD372" s="4"/>
       <c r="BE372" s="4"/>
     </row>
-    <row r="373" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -10817,7 +10817,7 @@
       <c r="BD373" s="4"/>
       <c r="BE373" s="4"/>
     </row>
-    <row r="374" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -10841,7 +10841,7 @@
       <c r="BD374" s="4"/>
       <c r="BE374" s="4"/>
     </row>
-    <row r="375" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -10865,7 +10865,7 @@
       <c r="BD375" s="4"/>
       <c r="BE375" s="4"/>
     </row>
-    <row r="376" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -10889,7 +10889,7 @@
       <c r="BD376" s="4"/>
       <c r="BE376" s="4"/>
     </row>
-    <row r="377" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -10913,7 +10913,7 @@
       <c r="BD377" s="4"/>
       <c r="BE377" s="4"/>
     </row>
-    <row r="378" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -10937,7 +10937,7 @@
       <c r="BD378" s="4"/>
       <c r="BE378" s="4"/>
     </row>
-    <row r="379" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -10961,7 +10961,7 @@
       <c r="BD379" s="4"/>
       <c r="BE379" s="4"/>
     </row>
-    <row r="380" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -10985,7 +10985,7 @@
       <c r="BD380" s="4"/>
       <c r="BE380" s="4"/>
     </row>
-    <row r="381" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -11009,7 +11009,7 @@
       <c r="BD381" s="4"/>
       <c r="BE381" s="4"/>
     </row>
-    <row r="382" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -11033,7 +11033,7 @@
       <c r="BD382" s="4"/>
       <c r="BE382" s="4"/>
     </row>
-    <row r="383" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -11057,7 +11057,7 @@
       <c r="BD383" s="4"/>
       <c r="BE383" s="4"/>
     </row>
-    <row r="384" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -11081,7 +11081,7 @@
       <c r="BD384" s="4"/>
       <c r="BE384" s="4"/>
     </row>
-    <row r="385" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -11105,7 +11105,7 @@
       <c r="BD385" s="4"/>
       <c r="BE385" s="4"/>
     </row>
-    <row r="386" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -11129,7 +11129,7 @@
       <c r="BD386" s="4"/>
       <c r="BE386" s="4"/>
     </row>
-    <row r="387" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -11153,7 +11153,7 @@
       <c r="BD387" s="4"/>
       <c r="BE387" s="4"/>
     </row>
-    <row r="388" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -11177,7 +11177,7 @@
       <c r="BD388" s="4"/>
       <c r="BE388" s="4"/>
     </row>
-    <row r="389" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -11201,7 +11201,7 @@
       <c r="BD389" s="4"/>
       <c r="BE389" s="4"/>
     </row>
-    <row r="390" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -11225,7 +11225,7 @@
       <c r="BD390" s="4"/>
       <c r="BE390" s="4"/>
     </row>
-    <row r="391" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -11249,7 +11249,7 @@
       <c r="BD391" s="4"/>
       <c r="BE391" s="4"/>
     </row>
-    <row r="392" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -11273,7 +11273,7 @@
       <c r="BD392" s="4"/>
       <c r="BE392" s="4"/>
     </row>
-    <row r="393" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -11297,7 +11297,7 @@
       <c r="BD393" s="4"/>
       <c r="BE393" s="4"/>
     </row>
-    <row r="394" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -11321,7 +11321,7 @@
       <c r="BD394" s="4"/>
       <c r="BE394" s="4"/>
     </row>
-    <row r="395" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -11345,7 +11345,7 @@
       <c r="BD395" s="4"/>
       <c r="BE395" s="4"/>
     </row>
-    <row r="396" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -11369,7 +11369,7 @@
       <c r="BD396" s="4"/>
       <c r="BE396" s="4"/>
     </row>
-    <row r="397" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -11393,7 +11393,7 @@
       <c r="BD397" s="4"/>
       <c r="BE397" s="4"/>
     </row>
-    <row r="398" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -11417,7 +11417,7 @@
       <c r="BD398" s="4"/>
       <c r="BE398" s="4"/>
     </row>
-    <row r="399" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -11441,7 +11441,7 @@
       <c r="BD399" s="4"/>
       <c r="BE399" s="4"/>
     </row>
-    <row r="400" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -11465,7 +11465,7 @@
       <c r="BD400" s="4"/>
       <c r="BE400" s="4"/>
     </row>
-    <row r="401" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -11489,7 +11489,7 @@
       <c r="BD401" s="4"/>
       <c r="BE401" s="4"/>
     </row>
-    <row r="402" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -11513,7 +11513,7 @@
       <c r="BD402" s="4"/>
       <c r="BE402" s="4"/>
     </row>
-    <row r="403" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -11537,7 +11537,7 @@
       <c r="BD403" s="4"/>
       <c r="BE403" s="4"/>
     </row>
-    <row r="404" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -11561,7 +11561,7 @@
       <c r="BD404" s="4"/>
       <c r="BE404" s="4"/>
     </row>
-    <row r="405" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -11585,7 +11585,7 @@
       <c r="BD405" s="4"/>
       <c r="BE405" s="4"/>
     </row>
-    <row r="406" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -11609,7 +11609,7 @@
       <c r="BD406" s="4"/>
       <c r="BE406" s="4"/>
     </row>
-    <row r="407" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -11633,7 +11633,7 @@
       <c r="BD407" s="4"/>
       <c r="BE407" s="4"/>
     </row>
-    <row r="408" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -11657,7 +11657,7 @@
       <c r="BD408" s="4"/>
       <c r="BE408" s="4"/>
     </row>
-    <row r="409" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -11681,7 +11681,7 @@
       <c r="BD409" s="4"/>
       <c r="BE409" s="4"/>
     </row>
-    <row r="410" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -11705,7 +11705,7 @@
       <c r="BD410" s="4"/>
       <c r="BE410" s="4"/>
     </row>
-    <row r="411" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -11729,7 +11729,7 @@
       <c r="BD411" s="4"/>
       <c r="BE411" s="4"/>
     </row>
-    <row r="412" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -11753,7 +11753,7 @@
       <c r="BD412" s="4"/>
       <c r="BE412" s="4"/>
     </row>
-    <row r="413" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -11777,7 +11777,7 @@
       <c r="BD413" s="4"/>
       <c r="BE413" s="4"/>
     </row>
-    <row r="414" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -11801,7 +11801,7 @@
       <c r="BD414" s="4"/>
       <c r="BE414" s="4"/>
     </row>
-    <row r="415" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -11825,7 +11825,7 @@
       <c r="BD415" s="4"/>
       <c r="BE415" s="4"/>
     </row>
-    <row r="416" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -11849,7 +11849,7 @@
       <c r="BD416" s="4"/>
       <c r="BE416" s="4"/>
     </row>
-    <row r="417" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -11873,7 +11873,7 @@
       <c r="BD417" s="4"/>
       <c r="BE417" s="4"/>
     </row>
-    <row r="418" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -11897,7 +11897,7 @@
       <c r="BD418" s="4"/>
       <c r="BE418" s="4"/>
     </row>
-    <row r="419" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -11921,7 +11921,7 @@
       <c r="BD419" s="4"/>
       <c r="BE419" s="4"/>
     </row>
-    <row r="420" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -11945,7 +11945,7 @@
       <c r="BD420" s="4"/>
       <c r="BE420" s="4"/>
     </row>
-    <row r="421" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -11969,7 +11969,7 @@
       <c r="BD421" s="4"/>
       <c r="BE421" s="4"/>
     </row>
-    <row r="422" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -11993,7 +11993,7 @@
       <c r="BD422" s="4"/>
       <c r="BE422" s="4"/>
     </row>
-    <row r="423" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -12017,7 +12017,7 @@
       <c r="BD423" s="4"/>
       <c r="BE423" s="4"/>
     </row>
-    <row r="424" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -12041,7 +12041,7 @@
       <c r="BD424" s="4"/>
       <c r="BE424" s="4"/>
     </row>
-    <row r="425" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -12065,7 +12065,7 @@
       <c r="BD425" s="4"/>
       <c r="BE425" s="4"/>
     </row>
-    <row r="426" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -12089,7 +12089,7 @@
       <c r="BD426" s="4"/>
       <c r="BE426" s="4"/>
     </row>
-    <row r="427" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -12113,7 +12113,7 @@
       <c r="BD427" s="4"/>
       <c r="BE427" s="4"/>
     </row>
-    <row r="428" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -12137,7 +12137,7 @@
       <c r="BD428" s="4"/>
       <c r="BE428" s="4"/>
     </row>
-    <row r="429" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -12161,7 +12161,7 @@
       <c r="BD429" s="4"/>
       <c r="BE429" s="4"/>
     </row>
-    <row r="430" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -12185,7 +12185,7 @@
       <c r="BD430" s="4"/>
       <c r="BE430" s="4"/>
     </row>
-    <row r="431" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -12209,7 +12209,7 @@
       <c r="BD431" s="4"/>
       <c r="BE431" s="4"/>
     </row>
-    <row r="432" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -12233,7 +12233,7 @@
       <c r="BD432" s="4"/>
       <c r="BE432" s="4"/>
     </row>
-    <row r="433" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -12257,7 +12257,7 @@
       <c r="BD433" s="4"/>
       <c r="BE433" s="4"/>
     </row>
-    <row r="434" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -12281,7 +12281,7 @@
       <c r="BD434" s="4"/>
       <c r="BE434" s="4"/>
     </row>
-    <row r="435" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -12305,7 +12305,7 @@
       <c r="BD435" s="4"/>
       <c r="BE435" s="4"/>
     </row>
-    <row r="436" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -12329,7 +12329,7 @@
       <c r="BD436" s="4"/>
       <c r="BE436" s="4"/>
     </row>
-    <row r="437" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -12353,7 +12353,7 @@
       <c r="BD437" s="4"/>
       <c r="BE437" s="4"/>
     </row>
-    <row r="438" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -12377,7 +12377,7 @@
       <c r="BD438" s="4"/>
       <c r="BE438" s="4"/>
     </row>
-    <row r="439" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -12401,7 +12401,7 @@
       <c r="BD439" s="4"/>
       <c r="BE439" s="4"/>
     </row>
-    <row r="440" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -12425,7 +12425,7 @@
       <c r="BD440" s="4"/>
       <c r="BE440" s="4"/>
     </row>
-    <row r="441" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -12449,7 +12449,7 @@
       <c r="BD441" s="4"/>
       <c r="BE441" s="4"/>
     </row>
-    <row r="442" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -12473,7 +12473,7 @@
       <c r="BD442" s="4"/>
       <c r="BE442" s="4"/>
     </row>
-    <row r="443" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -12497,7 +12497,7 @@
       <c r="BD443" s="4"/>
       <c r="BE443" s="4"/>
     </row>
-    <row r="444" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -12521,7 +12521,7 @@
       <c r="BD444" s="4"/>
       <c r="BE444" s="4"/>
     </row>
-    <row r="445" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -12545,7 +12545,7 @@
       <c r="BD445" s="4"/>
       <c r="BE445" s="4"/>
     </row>
-    <row r="446" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -12569,7 +12569,7 @@
       <c r="BD446" s="4"/>
       <c r="BE446" s="4"/>
     </row>
-    <row r="447" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -12593,7 +12593,7 @@
       <c r="BD447" s="4"/>
       <c r="BE447" s="4"/>
     </row>
-    <row r="448" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -12617,7 +12617,7 @@
       <c r="BD448" s="4"/>
       <c r="BE448" s="4"/>
     </row>
-    <row r="449" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -12641,7 +12641,7 @@
       <c r="BD449" s="4"/>
       <c r="BE449" s="4"/>
     </row>
-    <row r="450" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -12665,7 +12665,7 @@
       <c r="BD450" s="4"/>
       <c r="BE450" s="4"/>
     </row>
-    <row r="451" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -12689,7 +12689,7 @@
       <c r="BD451" s="4"/>
       <c r="BE451" s="4"/>
     </row>
-    <row r="452" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -12713,7 +12713,7 @@
       <c r="BD452" s="4"/>
       <c r="BE452" s="4"/>
     </row>
-    <row r="453" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -12737,7 +12737,7 @@
       <c r="BD453" s="4"/>
       <c r="BE453" s="4"/>
     </row>
-    <row r="454" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -12761,7 +12761,7 @@
       <c r="BD454" s="4"/>
       <c r="BE454" s="4"/>
     </row>
-    <row r="455" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -12785,7 +12785,7 @@
       <c r="BD455" s="4"/>
       <c r="BE455" s="4"/>
     </row>
-    <row r="456" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -12809,7 +12809,7 @@
       <c r="BD456" s="4"/>
       <c r="BE456" s="4"/>
     </row>
-    <row r="457" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -12833,7 +12833,7 @@
       <c r="BD457" s="4"/>
       <c r="BE457" s="4"/>
     </row>
-    <row r="458" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -12857,7 +12857,7 @@
       <c r="BD458" s="4"/>
       <c r="BE458" s="4"/>
     </row>
-    <row r="459" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -12881,7 +12881,7 @@
       <c r="BD459" s="4"/>
       <c r="BE459" s="4"/>
     </row>
-    <row r="460" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -12905,7 +12905,7 @@
       <c r="BD460" s="4"/>
       <c r="BE460" s="4"/>
     </row>
-    <row r="461" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -12929,7 +12929,7 @@
       <c r="BD461" s="4"/>
       <c r="BE461" s="4"/>
     </row>
-    <row r="462" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -12953,7 +12953,7 @@
       <c r="BD462" s="4"/>
       <c r="BE462" s="4"/>
     </row>
-    <row r="463" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -12977,7 +12977,7 @@
       <c r="BD463" s="4"/>
       <c r="BE463" s="4"/>
     </row>
-    <row r="464" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -13001,7 +13001,7 @@
       <c r="BD464" s="4"/>
       <c r="BE464" s="4"/>
     </row>
-    <row r="465" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -13025,7 +13025,7 @@
       <c r="BD465" s="4"/>
       <c r="BE465" s="4"/>
     </row>
-    <row r="466" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -13049,7 +13049,7 @@
       <c r="BD466" s="4"/>
       <c r="BE466" s="4"/>
     </row>
-    <row r="467" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -13073,7 +13073,7 @@
       <c r="BD467" s="4"/>
       <c r="BE467" s="4"/>
     </row>
-    <row r="468" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -13097,7 +13097,7 @@
       <c r="BD468" s="4"/>
       <c r="BE468" s="4"/>
     </row>
-    <row r="469" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -13121,7 +13121,7 @@
       <c r="BD469" s="4"/>
       <c r="BE469" s="4"/>
     </row>
-    <row r="470" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -13145,7 +13145,7 @@
       <c r="BD470" s="4"/>
       <c r="BE470" s="4"/>
     </row>
-    <row r="471" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -13169,7 +13169,7 @@
       <c r="BD471" s="4"/>
       <c r="BE471" s="4"/>
     </row>
-    <row r="472" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -13193,7 +13193,7 @@
       <c r="BD472" s="4"/>
       <c r="BE472" s="4"/>
     </row>
-    <row r="473" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -13217,7 +13217,7 @@
       <c r="BD473" s="4"/>
       <c r="BE473" s="4"/>
     </row>
-    <row r="474" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -13241,7 +13241,7 @@
       <c r="BD474" s="4"/>
       <c r="BE474" s="4"/>
     </row>
-    <row r="475" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -13265,7 +13265,7 @@
       <c r="BD475" s="4"/>
       <c r="BE475" s="4"/>
     </row>
-    <row r="476" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -13289,7 +13289,7 @@
       <c r="BD476" s="4"/>
       <c r="BE476" s="4"/>
     </row>
-    <row r="477" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -13313,7 +13313,7 @@
       <c r="BD477" s="4"/>
       <c r="BE477" s="4"/>
     </row>
-    <row r="478" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -13337,7 +13337,7 @@
       <c r="BD478" s="4"/>
       <c r="BE478" s="4"/>
     </row>
-    <row r="479" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -13361,7 +13361,7 @@
       <c r="BD479" s="4"/>
       <c r="BE479" s="4"/>
     </row>
-    <row r="480" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -13385,7 +13385,7 @@
       <c r="BD480" s="4"/>
       <c r="BE480" s="4"/>
     </row>
-    <row r="481" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -13409,7 +13409,7 @@
       <c r="BD481" s="4"/>
       <c r="BE481" s="4"/>
     </row>
-    <row r="482" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -13433,7 +13433,7 @@
       <c r="BD482" s="4"/>
       <c r="BE482" s="4"/>
     </row>
-    <row r="483" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -13457,7 +13457,7 @@
       <c r="BD483" s="4"/>
       <c r="BE483" s="4"/>
     </row>
-    <row r="484" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -13481,7 +13481,7 @@
       <c r="BD484" s="4"/>
       <c r="BE484" s="4"/>
     </row>
-    <row r="485" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -13505,7 +13505,7 @@
       <c r="BD485" s="4"/>
       <c r="BE485" s="4"/>
     </row>
-    <row r="486" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -13529,7 +13529,7 @@
       <c r="BD486" s="4"/>
       <c r="BE486" s="4"/>
     </row>
-    <row r="487" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -13553,7 +13553,7 @@
       <c r="BD487" s="4"/>
       <c r="BE487" s="4"/>
     </row>
-    <row r="488" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -13577,7 +13577,7 @@
       <c r="BD488" s="4"/>
       <c r="BE488" s="4"/>
     </row>
-    <row r="489" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -13601,7 +13601,7 @@
       <c r="BD489" s="4"/>
       <c r="BE489" s="4"/>
     </row>
-    <row r="490" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -13625,7 +13625,7 @@
       <c r="BD490" s="4"/>
       <c r="BE490" s="4"/>
     </row>
-    <row r="491" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -13649,7 +13649,7 @@
       <c r="BD491" s="4"/>
       <c r="BE491" s="4"/>
     </row>
-    <row r="492" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -13673,7 +13673,7 @@
       <c r="BD492" s="4"/>
       <c r="BE492" s="4"/>
     </row>
-    <row r="493" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -13697,7 +13697,7 @@
       <c r="BD493" s="4"/>
       <c r="BE493" s="4"/>
     </row>
-    <row r="494" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -13721,7 +13721,7 @@
       <c r="BD494" s="4"/>
       <c r="BE494" s="4"/>
     </row>
-    <row r="495" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -13745,7 +13745,7 @@
       <c r="BD495" s="4"/>
       <c r="BE495" s="4"/>
     </row>
-    <row r="496" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -13769,7 +13769,7 @@
       <c r="BD496" s="4"/>
       <c r="BE496" s="4"/>
     </row>
-    <row r="497" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -13793,7 +13793,7 @@
       <c r="BD497" s="4"/>
       <c r="BE497" s="4"/>
     </row>
-    <row r="498" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -13817,7 +13817,7 @@
       <c r="BD498" s="4"/>
       <c r="BE498" s="4"/>
     </row>
-    <row r="499" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -13841,7 +13841,7 @@
       <c r="BD499" s="4"/>
       <c r="BE499" s="4"/>
     </row>
-    <row r="500" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -13865,7 +13865,7 @@
       <c r="BD500" s="4"/>
       <c r="BE500" s="4"/>
     </row>
-    <row r="501" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -13889,7 +13889,7 @@
       <c r="BD501" s="4"/>
       <c r="BE501" s="4"/>
     </row>
-    <row r="502" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -13913,7 +13913,7 @@
       <c r="BD502" s="4"/>
       <c r="BE502" s="4"/>
     </row>
-    <row r="503" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -13937,7 +13937,7 @@
       <c r="BD503" s="4"/>
       <c r="BE503" s="4"/>
     </row>
-    <row r="504" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -13961,7 +13961,7 @@
       <c r="BD504" s="4"/>
       <c r="BE504" s="4"/>
     </row>
-    <row r="505" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -13985,7 +13985,7 @@
       <c r="BD505" s="4"/>
       <c r="BE505" s="4"/>
     </row>
-    <row r="506" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -14009,7 +14009,7 @@
       <c r="BD506" s="4"/>
       <c r="BE506" s="4"/>
     </row>
-    <row r="507" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -14033,7 +14033,7 @@
       <c r="BD507" s="4"/>
       <c r="BE507" s="4"/>
     </row>
-    <row r="508" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -14057,7 +14057,7 @@
       <c r="BD508" s="4"/>
       <c r="BE508" s="4"/>
     </row>
-    <row r="509" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -14081,7 +14081,7 @@
       <c r="BD509" s="4"/>
       <c r="BE509" s="4"/>
     </row>
-    <row r="510" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -14105,7 +14105,7 @@
       <c r="BD510" s="4"/>
       <c r="BE510" s="4"/>
     </row>
-    <row r="511" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -14129,7 +14129,7 @@
       <c r="BD511" s="4"/>
       <c r="BE511" s="4"/>
     </row>
-    <row r="512" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -14153,7 +14153,7 @@
       <c r="BD512" s="4"/>
       <c r="BE512" s="4"/>
     </row>
-    <row r="513" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -14177,7 +14177,7 @@
       <c r="BD513" s="4"/>
       <c r="BE513" s="4"/>
     </row>
-    <row r="514" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -14201,7 +14201,7 @@
       <c r="BD514" s="4"/>
       <c r="BE514" s="4"/>
     </row>
-    <row r="515" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -14225,7 +14225,7 @@
       <c r="BD515" s="4"/>
       <c r="BE515" s="4"/>
     </row>
-    <row r="516" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -14249,7 +14249,7 @@
       <c r="BD516" s="4"/>
       <c r="BE516" s="4"/>
     </row>
-    <row r="517" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -14273,7 +14273,7 @@
       <c r="BD517" s="4"/>
       <c r="BE517" s="4"/>
     </row>
-    <row r="518" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -14297,7 +14297,7 @@
       <c r="BD518" s="4"/>
       <c r="BE518" s="4"/>
     </row>
-    <row r="519" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -14321,7 +14321,7 @@
       <c r="BD519" s="4"/>
       <c r="BE519" s="4"/>
     </row>
-    <row r="520" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -14345,7 +14345,7 @@
       <c r="BD520" s="4"/>
       <c r="BE520" s="4"/>
     </row>
-    <row r="521" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -14369,7 +14369,7 @@
       <c r="BD521" s="4"/>
       <c r="BE521" s="4"/>
     </row>
-    <row r="522" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -14393,7 +14393,7 @@
       <c r="BD522" s="4"/>
       <c r="BE522" s="4"/>
     </row>
-    <row r="523" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -14417,7 +14417,7 @@
       <c r="BD523" s="4"/>
       <c r="BE523" s="4"/>
     </row>
-    <row r="524" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -14441,7 +14441,7 @@
       <c r="BD524" s="4"/>
       <c r="BE524" s="4"/>
     </row>
-    <row r="525" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -14465,7 +14465,7 @@
       <c r="BD525" s="4"/>
       <c r="BE525" s="4"/>
     </row>
-    <row r="526" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -14489,7 +14489,7 @@
       <c r="BD526" s="4"/>
       <c r="BE526" s="4"/>
     </row>
-    <row r="527" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -14513,7 +14513,7 @@
       <c r="BD527" s="4"/>
       <c r="BE527" s="4"/>
     </row>
-    <row r="528" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -14537,7 +14537,7 @@
       <c r="BD528" s="4"/>
       <c r="BE528" s="4"/>
     </row>
-    <row r="529" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -14561,7 +14561,7 @@
       <c r="BD529" s="4"/>
       <c r="BE529" s="4"/>
     </row>
-    <row r="530" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -14585,7 +14585,7 @@
       <c r="BD530" s="4"/>
       <c r="BE530" s="4"/>
     </row>
-    <row r="531" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -14609,7 +14609,7 @@
       <c r="BD531" s="4"/>
       <c r="BE531" s="4"/>
     </row>
-    <row r="532" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -14633,7 +14633,7 @@
       <c r="BD532" s="4"/>
       <c r="BE532" s="4"/>
     </row>
-    <row r="533" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -14657,7 +14657,7 @@
       <c r="BD533" s="4"/>
       <c r="BE533" s="4"/>
     </row>
-    <row r="534" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -14681,7 +14681,7 @@
       <c r="BD534" s="4"/>
       <c r="BE534" s="4"/>
     </row>
-    <row r="535" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -14705,7 +14705,7 @@
       <c r="BD535" s="4"/>
       <c r="BE535" s="4"/>
     </row>
-    <row r="536" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -14729,7 +14729,7 @@
       <c r="BD536" s="4"/>
       <c r="BE536" s="4"/>
     </row>
-    <row r="537" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -14753,7 +14753,7 @@
       <c r="BD537" s="4"/>
       <c r="BE537" s="4"/>
     </row>
-    <row r="538" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -14777,7 +14777,7 @@
       <c r="BD538" s="4"/>
       <c r="BE538" s="4"/>
     </row>
-    <row r="539" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -14801,7 +14801,7 @@
       <c r="BD539" s="4"/>
       <c r="BE539" s="4"/>
     </row>
-    <row r="540" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -14825,7 +14825,7 @@
       <c r="BD540" s="4"/>
       <c r="BE540" s="4"/>
     </row>
-    <row r="541" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -14849,7 +14849,7 @@
       <c r="BD541" s="4"/>
       <c r="BE541" s="4"/>
     </row>
-    <row r="542" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -14873,7 +14873,7 @@
       <c r="BD542" s="4"/>
       <c r="BE542" s="4"/>
     </row>
-    <row r="543" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -14897,7 +14897,7 @@
       <c r="BD543" s="4"/>
       <c r="BE543" s="4"/>
     </row>
-    <row r="544" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -14921,7 +14921,7 @@
       <c r="BD544" s="4"/>
       <c r="BE544" s="4"/>
     </row>
-    <row r="545" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -14945,7 +14945,7 @@
       <c r="BD545" s="4"/>
       <c r="BE545" s="4"/>
     </row>
-    <row r="546" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -14969,7 +14969,7 @@
       <c r="BD546" s="4"/>
       <c r="BE546" s="4"/>
     </row>
-    <row r="547" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -14993,7 +14993,7 @@
       <c r="BD547" s="4"/>
       <c r="BE547" s="4"/>
     </row>
-    <row r="548" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -15017,7 +15017,7 @@
       <c r="BD548" s="4"/>
       <c r="BE548" s="4"/>
     </row>
-    <row r="549" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -15041,7 +15041,7 @@
       <c r="BD549" s="4"/>
       <c r="BE549" s="4"/>
     </row>
-    <row r="550" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -15065,7 +15065,7 @@
       <c r="BD550" s="4"/>
       <c r="BE550" s="4"/>
     </row>
-    <row r="551" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -15089,7 +15089,7 @@
       <c r="BD551" s="4"/>
       <c r="BE551" s="4"/>
     </row>
-    <row r="552" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -15113,7 +15113,7 @@
       <c r="BD552" s="4"/>
       <c r="BE552" s="4"/>
     </row>
-    <row r="553" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -15137,7 +15137,7 @@
       <c r="BD553" s="4"/>
       <c r="BE553" s="4"/>
     </row>
-    <row r="554" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -15161,7 +15161,7 @@
       <c r="BD554" s="4"/>
       <c r="BE554" s="4"/>
     </row>
-    <row r="555" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -15185,7 +15185,7 @@
       <c r="BD555" s="4"/>
       <c r="BE555" s="4"/>
     </row>
-    <row r="556" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -15209,7 +15209,7 @@
       <c r="BD556" s="4"/>
       <c r="BE556" s="4"/>
     </row>
-    <row r="557" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -15233,7 +15233,7 @@
       <c r="BD557" s="4"/>
       <c r="BE557" s="4"/>
     </row>
-    <row r="558" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -15257,7 +15257,7 @@
       <c r="BD558" s="4"/>
       <c r="BE558" s="4"/>
     </row>
-    <row r="559" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -15281,7 +15281,7 @@
       <c r="BD559" s="4"/>
       <c r="BE559" s="4"/>
     </row>
-    <row r="560" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -15305,7 +15305,7 @@
       <c r="BD560" s="4"/>
       <c r="BE560" s="4"/>
     </row>
-    <row r="561" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -15329,7 +15329,7 @@
       <c r="BD561" s="4"/>
       <c r="BE561" s="4"/>
     </row>
-    <row r="562" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -15353,7 +15353,7 @@
       <c r="BD562" s="4"/>
       <c r="BE562" s="4"/>
     </row>
-    <row r="563" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -15377,7 +15377,7 @@
       <c r="BD563" s="4"/>
       <c r="BE563" s="4"/>
     </row>
-    <row r="564" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -15401,7 +15401,7 @@
       <c r="BD564" s="4"/>
       <c r="BE564" s="4"/>
     </row>
-    <row r="565" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -15425,7 +15425,7 @@
       <c r="BD565" s="4"/>
       <c r="BE565" s="4"/>
     </row>
-    <row r="566" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -15449,7 +15449,7 @@
       <c r="BD566" s="4"/>
       <c r="BE566" s="4"/>
     </row>
-    <row r="567" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -15473,7 +15473,7 @@
       <c r="BD567" s="4"/>
       <c r="BE567" s="4"/>
     </row>
-    <row r="568" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -15497,7 +15497,7 @@
       <c r="BD568" s="4"/>
       <c r="BE568" s="4"/>
     </row>
-    <row r="569" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -15521,7 +15521,7 @@
       <c r="BD569" s="4"/>
       <c r="BE569" s="4"/>
     </row>
-    <row r="570" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -15545,7 +15545,7 @@
       <c r="BD570" s="4"/>
       <c r="BE570" s="4"/>
     </row>
-    <row r="571" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -15569,7 +15569,7 @@
       <c r="BD571" s="4"/>
       <c r="BE571" s="4"/>
     </row>
-    <row r="572" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -15593,7 +15593,7 @@
       <c r="BD572" s="4"/>
       <c r="BE572" s="4"/>
     </row>
-    <row r="573" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -15617,7 +15617,7 @@
       <c r="BD573" s="4"/>
       <c r="BE573" s="4"/>
     </row>
-    <row r="574" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -15641,7 +15641,7 @@
       <c r="BD574" s="4"/>
       <c r="BE574" s="4"/>
     </row>
-    <row r="575" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -15665,7 +15665,7 @@
       <c r="BD575" s="4"/>
       <c r="BE575" s="4"/>
     </row>
-    <row r="576" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -15689,7 +15689,7 @@
       <c r="BD576" s="4"/>
       <c r="BE576" s="4"/>
     </row>
-    <row r="577" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -15713,7 +15713,7 @@
       <c r="BD577" s="4"/>
       <c r="BE577" s="4"/>
     </row>
-    <row r="578" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -15737,7 +15737,7 @@
       <c r="BD578" s="4"/>
       <c r="BE578" s="4"/>
     </row>
-    <row r="579" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -15761,7 +15761,7 @@
       <c r="BD579" s="4"/>
       <c r="BE579" s="4"/>
     </row>
-    <row r="580" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -15785,7 +15785,7 @@
       <c r="BD580" s="4"/>
       <c r="BE580" s="4"/>
     </row>
-    <row r="581" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -15809,7 +15809,7 @@
       <c r="BD581" s="4"/>
       <c r="BE581" s="4"/>
     </row>
-    <row r="582" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -15833,7 +15833,7 @@
       <c r="BD582" s="4"/>
       <c r="BE582" s="4"/>
     </row>
-    <row r="583" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -15857,7 +15857,7 @@
       <c r="BD583" s="4"/>
       <c r="BE583" s="4"/>
     </row>
-    <row r="584" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -15881,7 +15881,7 @@
       <c r="BD584" s="4"/>
       <c r="BE584" s="4"/>
     </row>
-    <row r="585" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -15905,7 +15905,7 @@
       <c r="BD585" s="4"/>
       <c r="BE585" s="4"/>
     </row>
-    <row r="586" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -15929,7 +15929,7 @@
       <c r="BD586" s="4"/>
       <c r="BE586" s="4"/>
     </row>
-    <row r="587" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -15953,7 +15953,7 @@
       <c r="BD587" s="4"/>
       <c r="BE587" s="4"/>
     </row>
-    <row r="588" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -15977,7 +15977,7 @@
       <c r="BD588" s="4"/>
       <c r="BE588" s="4"/>
     </row>
-    <row r="589" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -16001,7 +16001,7 @@
       <c r="BD589" s="4"/>
       <c r="BE589" s="4"/>
     </row>
-    <row r="590" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="4"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -16025,7 +16025,7 @@
       <c r="BD590" s="4"/>
       <c r="BE590" s="4"/>
     </row>
-    <row r="591" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="4"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -16049,7 +16049,7 @@
       <c r="BD591" s="4"/>
       <c r="BE591" s="4"/>
     </row>
-    <row r="592" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="4"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -16073,7 +16073,7 @@
       <c r="BD592" s="4"/>
       <c r="BE592" s="4"/>
     </row>
-    <row r="593" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="4"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -16097,7 +16097,7 @@
       <c r="BD593" s="4"/>
       <c r="BE593" s="4"/>
     </row>
-    <row r="594" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="4"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -16121,7 +16121,7 @@
       <c r="BD594" s="4"/>
       <c r="BE594" s="4"/>
     </row>
-    <row r="595" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="4"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -16145,7 +16145,7 @@
       <c r="BD595" s="4"/>
       <c r="BE595" s="4"/>
     </row>
-    <row r="596" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -16169,7 +16169,7 @@
       <c r="BD596" s="4"/>
       <c r="BE596" s="4"/>
     </row>
-    <row r="597" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -16193,7 +16193,7 @@
       <c r="BD597" s="4"/>
       <c r="BE597" s="4"/>
     </row>
-    <row r="598" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -16217,7 +16217,7 @@
       <c r="BD598" s="4"/>
       <c r="BE598" s="4"/>
     </row>
-    <row r="599" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -16241,7 +16241,7 @@
       <c r="BD599" s="4"/>
       <c r="BE599" s="4"/>
     </row>
-    <row r="600" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -16265,7 +16265,7 @@
       <c r="BD600" s="4"/>
       <c r="BE600" s="4"/>
     </row>
-    <row r="601" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -16289,7 +16289,7 @@
       <c r="BD601" s="4"/>
       <c r="BE601" s="4"/>
     </row>
-    <row r="602" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -16313,7 +16313,7 @@
       <c r="BD602" s="4"/>
       <c r="BE602" s="4"/>
     </row>
-    <row r="603" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -16337,7 +16337,7 @@
       <c r="BD603" s="4"/>
       <c r="BE603" s="4"/>
     </row>
-    <row r="604" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -16361,7 +16361,7 @@
       <c r="BD604" s="4"/>
       <c r="BE604" s="4"/>
     </row>
-    <row r="605" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -16385,7 +16385,7 @@
       <c r="BD605" s="4"/>
       <c r="BE605" s="4"/>
     </row>
-    <row r="606" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -16409,7 +16409,7 @@
       <c r="BD606" s="4"/>
       <c r="BE606" s="4"/>
     </row>
-    <row r="607" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -16433,7 +16433,7 @@
       <c r="BD607" s="4"/>
       <c r="BE607" s="4"/>
     </row>
-    <row r="608" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -16457,7 +16457,7 @@
       <c r="BD608" s="4"/>
       <c r="BE608" s="4"/>
     </row>
-    <row r="609" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -16481,7 +16481,7 @@
       <c r="BD609" s="4"/>
       <c r="BE609" s="4"/>
     </row>
-    <row r="610" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -16505,7 +16505,7 @@
       <c r="BD610" s="4"/>
       <c r="BE610" s="4"/>
     </row>
-    <row r="611" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -16529,7 +16529,7 @@
       <c r="BD611" s="4"/>
       <c r="BE611" s="4"/>
     </row>
-    <row r="612" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -16553,7 +16553,7 @@
       <c r="BD612" s="4"/>
       <c r="BE612" s="4"/>
     </row>
-    <row r="613" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -16577,7 +16577,7 @@
       <c r="BD613" s="4"/>
       <c r="BE613" s="4"/>
     </row>
-    <row r="614" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -16601,7 +16601,7 @@
       <c r="BD614" s="4"/>
       <c r="BE614" s="4"/>
     </row>
-    <row r="615" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -16625,7 +16625,7 @@
       <c r="BD615" s="4"/>
       <c r="BE615" s="4"/>
     </row>
-    <row r="616" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -16649,7 +16649,7 @@
       <c r="BD616" s="4"/>
       <c r="BE616" s="4"/>
     </row>
-    <row r="617" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -16673,7 +16673,7 @@
       <c r="BD617" s="4"/>
       <c r="BE617" s="4"/>
     </row>
-    <row r="618" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -16697,7 +16697,7 @@
       <c r="BD618" s="4"/>
       <c r="BE618" s="4"/>
     </row>
-    <row r="619" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -16721,7 +16721,7 @@
       <c r="BD619" s="4"/>
       <c r="BE619" s="4"/>
     </row>
-    <row r="620" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -16745,7 +16745,7 @@
       <c r="BD620" s="4"/>
       <c r="BE620" s="4"/>
     </row>
-    <row r="621" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -16769,7 +16769,7 @@
       <c r="BD621" s="4"/>
       <c r="BE621" s="4"/>
     </row>
-    <row r="622" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -16793,7 +16793,7 @@
       <c r="BD622" s="4"/>
       <c r="BE622" s="4"/>
     </row>
-    <row r="623" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -16817,7 +16817,7 @@
       <c r="BD623" s="4"/>
       <c r="BE623" s="4"/>
     </row>
-    <row r="624" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -16841,7 +16841,7 @@
       <c r="BD624" s="4"/>
       <c r="BE624" s="4"/>
     </row>
-    <row r="625" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -16865,7 +16865,7 @@
       <c r="BD625" s="4"/>
       <c r="BE625" s="4"/>
     </row>
-    <row r="626" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -16889,7 +16889,7 @@
       <c r="BD626" s="4"/>
       <c r="BE626" s="4"/>
     </row>
-    <row r="627" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -16913,7 +16913,7 @@
       <c r="BD627" s="4"/>
       <c r="BE627" s="4"/>
     </row>
-    <row r="628" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -16937,7 +16937,7 @@
       <c r="BD628" s="4"/>
       <c r="BE628" s="4"/>
     </row>
-    <row r="629" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -16961,7 +16961,7 @@
       <c r="BD629" s="4"/>
       <c r="BE629" s="4"/>
     </row>
-    <row r="630" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -16985,7 +16985,7 @@
       <c r="BD630" s="4"/>
       <c r="BE630" s="4"/>
     </row>
-    <row r="631" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -17009,7 +17009,7 @@
       <c r="BD631" s="4"/>
       <c r="BE631" s="4"/>
     </row>
-    <row r="632" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -17033,7 +17033,7 @@
       <c r="BD632" s="4"/>
       <c r="BE632" s="4"/>
     </row>
-    <row r="633" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -17057,7 +17057,7 @@
       <c r="BD633" s="4"/>
       <c r="BE633" s="4"/>
     </row>
-    <row r="634" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -17081,7 +17081,7 @@
       <c r="BD634" s="4"/>
       <c r="BE634" s="4"/>
     </row>
-    <row r="635" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -17105,7 +17105,7 @@
       <c r="BD635" s="4"/>
       <c r="BE635" s="4"/>
     </row>
-    <row r="636" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -17129,7 +17129,7 @@
       <c r="BD636" s="4"/>
       <c r="BE636" s="4"/>
     </row>
-    <row r="637" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -17153,7 +17153,7 @@
       <c r="BD637" s="4"/>
       <c r="BE637" s="4"/>
     </row>
-    <row r="638" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -17177,7 +17177,7 @@
       <c r="BD638" s="4"/>
       <c r="BE638" s="4"/>
     </row>
-    <row r="639" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -17201,7 +17201,7 @@
       <c r="BD639" s="4"/>
       <c r="BE639" s="4"/>
     </row>
-    <row r="640" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -17225,7 +17225,7 @@
       <c r="BD640" s="4"/>
       <c r="BE640" s="4"/>
     </row>
-    <row r="641" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -17249,7 +17249,7 @@
       <c r="BD641" s="4"/>
       <c r="BE641" s="4"/>
     </row>
-    <row r="642" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -17273,7 +17273,7 @@
       <c r="BD642" s="4"/>
       <c r="BE642" s="4"/>
     </row>
-    <row r="643" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -17297,7 +17297,7 @@
       <c r="BD643" s="4"/>
       <c r="BE643" s="4"/>
     </row>
-    <row r="644" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -17321,7 +17321,7 @@
       <c r="BD644" s="4"/>
       <c r="BE644" s="4"/>
     </row>
-    <row r="645" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -17345,7 +17345,7 @@
       <c r="BD645" s="4"/>
       <c r="BE645" s="4"/>
     </row>
-    <row r="646" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -17369,7 +17369,7 @@
       <c r="BD646" s="4"/>
       <c r="BE646" s="4"/>
     </row>
-    <row r="647" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -17393,7 +17393,7 @@
       <c r="BD647" s="4"/>
       <c r="BE647" s="4"/>
     </row>
-    <row r="648" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -17417,7 +17417,7 @@
       <c r="BD648" s="4"/>
       <c r="BE648" s="4"/>
     </row>
-    <row r="649" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -17441,7 +17441,7 @@
       <c r="BD649" s="4"/>
       <c r="BE649" s="4"/>
     </row>
-    <row r="650" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -17465,7 +17465,7 @@
       <c r="BD650" s="4"/>
       <c r="BE650" s="4"/>
     </row>
-    <row r="651" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -17489,7 +17489,7 @@
       <c r="BD651" s="4"/>
       <c r="BE651" s="4"/>
     </row>
-    <row r="652" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -17513,7 +17513,7 @@
       <c r="BD652" s="4"/>
       <c r="BE652" s="4"/>
     </row>
-    <row r="653" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -17537,7 +17537,7 @@
       <c r="BD653" s="4"/>
       <c r="BE653" s="4"/>
     </row>
-    <row r="654" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -17561,7 +17561,7 @@
       <c r="BD654" s="4"/>
       <c r="BE654" s="4"/>
     </row>
-    <row r="655" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -17585,7 +17585,7 @@
       <c r="BD655" s="4"/>
       <c r="BE655" s="4"/>
     </row>
-    <row r="656" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -17609,7 +17609,7 @@
       <c r="BD656" s="4"/>
       <c r="BE656" s="4"/>
     </row>
-    <row r="657" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -17633,7 +17633,7 @@
       <c r="BD657" s="4"/>
       <c r="BE657" s="4"/>
     </row>
-    <row r="658" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -17657,7 +17657,7 @@
       <c r="BD658" s="4"/>
       <c r="BE658" s="4"/>
     </row>
-    <row r="659" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -17681,7 +17681,7 @@
       <c r="BD659" s="4"/>
       <c r="BE659" s="4"/>
     </row>
-    <row r="660" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="4"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -17705,7 +17705,7 @@
       <c r="BD660" s="4"/>
       <c r="BE660" s="4"/>
     </row>
-    <row r="661" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="4"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -17729,7 +17729,7 @@
       <c r="BD661" s="4"/>
       <c r="BE661" s="4"/>
     </row>
-    <row r="662" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="4"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -17753,7 +17753,7 @@
       <c r="BD662" s="4"/>
       <c r="BE662" s="4"/>
     </row>
-    <row r="663" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="4"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -17777,7 +17777,7 @@
       <c r="BD663" s="4"/>
       <c r="BE663" s="4"/>
     </row>
-    <row r="664" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="4"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -17801,7 +17801,7 @@
       <c r="BD664" s="4"/>
       <c r="BE664" s="4"/>
     </row>
-    <row r="665" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="4"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -17825,7 +17825,7 @@
       <c r="BD665" s="4"/>
       <c r="BE665" s="4"/>
     </row>
-    <row r="666" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -17849,7 +17849,7 @@
       <c r="BD666" s="4"/>
       <c r="BE666" s="4"/>
     </row>
-    <row r="667" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="4"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -17873,7 +17873,7 @@
       <c r="BD667" s="4"/>
       <c r="BE667" s="4"/>
     </row>
-    <row r="668" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="4"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -17897,7 +17897,7 @@
       <c r="BD668" s="4"/>
       <c r="BE668" s="4"/>
     </row>
-    <row r="669" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -17921,7 +17921,7 @@
       <c r="BD669" s="4"/>
       <c r="BE669" s="4"/>
     </row>
-    <row r="670" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -17945,7 +17945,7 @@
       <c r="BD670" s="4"/>
       <c r="BE670" s="4"/>
     </row>
-    <row r="671" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -17969,7 +17969,7 @@
       <c r="BD671" s="4"/>
       <c r="BE671" s="4"/>
     </row>
-    <row r="672" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="4"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -17993,7 +17993,7 @@
       <c r="BD672" s="4"/>
       <c r="BE672" s="4"/>
     </row>
-    <row r="673" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="4"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -18017,7 +18017,7 @@
       <c r="BD673" s="4"/>
       <c r="BE673" s="4"/>
     </row>
-    <row r="674" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -18041,7 +18041,7 @@
       <c r="BD674" s="4"/>
       <c r="BE674" s="4"/>
     </row>
-    <row r="675" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="4"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -18065,7 +18065,7 @@
       <c r="BD675" s="4"/>
       <c r="BE675" s="4"/>
     </row>
-    <row r="676" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="4"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -18089,7 +18089,7 @@
       <c r="BD676" s="4"/>
       <c r="BE676" s="4"/>
     </row>
-    <row r="677" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="4"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -18113,7 +18113,7 @@
       <c r="BD677" s="4"/>
       <c r="BE677" s="4"/>
     </row>
-    <row r="678" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="4"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -18137,7 +18137,7 @@
       <c r="BD678" s="4"/>
       <c r="BE678" s="4"/>
     </row>
-    <row r="679" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="4"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -18161,7 +18161,7 @@
       <c r="BD679" s="4"/>
       <c r="BE679" s="4"/>
     </row>
-    <row r="680" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="4"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -18185,7 +18185,7 @@
       <c r="BD680" s="4"/>
       <c r="BE680" s="4"/>
     </row>
-    <row r="681" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="4"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -18209,7 +18209,7 @@
       <c r="BD681" s="4"/>
       <c r="BE681" s="4"/>
     </row>
-    <row r="682" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="4"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -18233,7 +18233,7 @@
       <c r="BD682" s="4"/>
       <c r="BE682" s="4"/>
     </row>
-    <row r="683" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="4"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -18257,7 +18257,7 @@
       <c r="BD683" s="4"/>
       <c r="BE683" s="4"/>
     </row>
-    <row r="684" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="4"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -18281,7 +18281,7 @@
       <c r="BD684" s="4"/>
       <c r="BE684" s="4"/>
     </row>
-    <row r="685" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="4"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -18305,7 +18305,7 @@
       <c r="BD685" s="4"/>
       <c r="BE685" s="4"/>
     </row>
-    <row r="686" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="4"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -18329,7 +18329,7 @@
       <c r="BD686" s="4"/>
       <c r="BE686" s="4"/>
     </row>
-    <row r="687" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="4"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -18353,7 +18353,7 @@
       <c r="BD687" s="4"/>
       <c r="BE687" s="4"/>
     </row>
-    <row r="688" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="4"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -18377,7 +18377,7 @@
       <c r="BD688" s="4"/>
       <c r="BE688" s="4"/>
     </row>
-    <row r="689" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -18401,7 +18401,7 @@
       <c r="BD689" s="4"/>
       <c r="BE689" s="4"/>
     </row>
-    <row r="690" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -18425,7 +18425,7 @@
       <c r="BD690" s="4"/>
       <c r="BE690" s="4"/>
     </row>
-    <row r="691" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -18449,7 +18449,7 @@
       <c r="BD691" s="4"/>
       <c r="BE691" s="4"/>
     </row>
-    <row r="692" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -18473,7 +18473,7 @@
       <c r="BD692" s="4"/>
       <c r="BE692" s="4"/>
     </row>
-    <row r="693" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -18497,7 +18497,7 @@
       <c r="BD693" s="4"/>
       <c r="BE693" s="4"/>
     </row>
-    <row r="694" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="4"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -18521,7 +18521,7 @@
       <c r="BD694" s="4"/>
       <c r="BE694" s="4"/>
     </row>
-    <row r="695" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="4"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -18545,7 +18545,7 @@
       <c r="BD695" s="4"/>
       <c r="BE695" s="4"/>
     </row>
-    <row r="696" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A696" s="4"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -18569,7 +18569,7 @@
       <c r="BD696" s="4"/>
       <c r="BE696" s="4"/>
     </row>
-    <row r="697" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="4"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -18593,7 +18593,7 @@
       <c r="BD697" s="4"/>
       <c r="BE697" s="4"/>
     </row>
-    <row r="698" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="4"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -18617,7 +18617,7 @@
       <c r="BD698" s="4"/>
       <c r="BE698" s="4"/>
     </row>
-    <row r="699" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="4"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -18641,7 +18641,7 @@
       <c r="BD699" s="4"/>
       <c r="BE699" s="4"/>
     </row>
-    <row r="700" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="4"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -18665,7 +18665,7 @@
       <c r="BD700" s="4"/>
       <c r="BE700" s="4"/>
     </row>
-    <row r="701" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="4"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -18689,7 +18689,7 @@
       <c r="BD701" s="4"/>
       <c r="BE701" s="4"/>
     </row>
-    <row r="702" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="4"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -18713,7 +18713,7 @@
       <c r="BD702" s="4"/>
       <c r="BE702" s="4"/>
     </row>
-    <row r="703" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="4"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -18737,7 +18737,7 @@
       <c r="BD703" s="4"/>
       <c r="BE703" s="4"/>
     </row>
-    <row r="704" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="4"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -18761,7 +18761,7 @@
       <c r="BD704" s="4"/>
       <c r="BE704" s="4"/>
     </row>
-    <row r="705" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="4"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -18785,7 +18785,7 @@
       <c r="BD705" s="4"/>
       <c r="BE705" s="4"/>
     </row>
-    <row r="706" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="4"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -18809,7 +18809,7 @@
       <c r="BD706" s="4"/>
       <c r="BE706" s="4"/>
     </row>
-    <row r="707" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="4"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -18833,7 +18833,7 @@
       <c r="BD707" s="4"/>
       <c r="BE707" s="4"/>
     </row>
-    <row r="708" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="4"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -18857,7 +18857,7 @@
       <c r="BD708" s="4"/>
       <c r="BE708" s="4"/>
     </row>
-    <row r="709" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="4"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -18881,7 +18881,7 @@
       <c r="BD709" s="4"/>
       <c r="BE709" s="4"/>
     </row>
-    <row r="710" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="4"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -18905,7 +18905,7 @@
       <c r="BD710" s="4"/>
       <c r="BE710" s="4"/>
     </row>
-    <row r="711" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="4"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -18929,7 +18929,7 @@
       <c r="BD711" s="4"/>
       <c r="BE711" s="4"/>
     </row>
-    <row r="712" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="4"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -18953,7 +18953,7 @@
       <c r="BD712" s="4"/>
       <c r="BE712" s="4"/>
     </row>
-    <row r="713" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="4"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -18977,7 +18977,7 @@
       <c r="BD713" s="4"/>
       <c r="BE713" s="4"/>
     </row>
-    <row r="714" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="4"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -19001,7 +19001,7 @@
       <c r="BD714" s="4"/>
       <c r="BE714" s="4"/>
     </row>
-    <row r="715" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="4"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -19025,7 +19025,7 @@
       <c r="BD715" s="4"/>
       <c r="BE715" s="4"/>
     </row>
-    <row r="716" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="4"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -19049,7 +19049,7 @@
       <c r="BD716" s="4"/>
       <c r="BE716" s="4"/>
     </row>
-    <row r="717" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="4"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -19073,7 +19073,7 @@
       <c r="BD717" s="4"/>
       <c r="BE717" s="4"/>
     </row>
-    <row r="718" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="4"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -19097,7 +19097,7 @@
       <c r="BD718" s="4"/>
       <c r="BE718" s="4"/>
     </row>
-    <row r="719" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="4"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -19121,7 +19121,7 @@
       <c r="BD719" s="4"/>
       <c r="BE719" s="4"/>
     </row>
-    <row r="720" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="4"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -19145,7 +19145,7 @@
       <c r="BD720" s="4"/>
       <c r="BE720" s="4"/>
     </row>
-    <row r="721" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="4"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -19169,7 +19169,7 @@
       <c r="BD721" s="4"/>
       <c r="BE721" s="4"/>
     </row>
-    <row r="722" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="4"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -19193,7 +19193,7 @@
       <c r="BD722" s="4"/>
       <c r="BE722" s="4"/>
     </row>
-    <row r="723" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="4"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -19217,7 +19217,7 @@
       <c r="BD723" s="4"/>
       <c r="BE723" s="4"/>
     </row>
-    <row r="724" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="4"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -19241,7 +19241,7 @@
       <c r="BD724" s="4"/>
       <c r="BE724" s="4"/>
     </row>
-    <row r="725" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="4"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -19265,7 +19265,7 @@
       <c r="BD725" s="4"/>
       <c r="BE725" s="4"/>
     </row>
-    <row r="726" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -19289,7 +19289,7 @@
       <c r="BD726" s="4"/>
       <c r="BE726" s="4"/>
     </row>
-    <row r="727" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -19313,7 +19313,7 @@
       <c r="BD727" s="4"/>
       <c r="BE727" s="4"/>
     </row>
-    <row r="728" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -19337,7 +19337,7 @@
       <c r="BD728" s="4"/>
       <c r="BE728" s="4"/>
     </row>
-    <row r="729" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="4"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -19361,7 +19361,7 @@
       <c r="BD729" s="4"/>
       <c r="BE729" s="4"/>
     </row>
-    <row r="730" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="4"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -19385,7 +19385,7 @@
       <c r="BD730" s="4"/>
       <c r="BE730" s="4"/>
     </row>
-    <row r="731" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="4"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -19409,7 +19409,7 @@
       <c r="BD731" s="4"/>
       <c r="BE731" s="4"/>
     </row>
-    <row r="732" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="4"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -19433,7 +19433,7 @@
       <c r="BD732" s="4"/>
       <c r="BE732" s="4"/>
     </row>
-    <row r="733" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A733" s="4"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -19457,7 +19457,7 @@
       <c r="BD733" s="4"/>
       <c r="BE733" s="4"/>
     </row>
-    <row r="734" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A734" s="4"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -19481,7 +19481,7 @@
       <c r="BD734" s="4"/>
       <c r="BE734" s="4"/>
     </row>
-    <row r="735" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A735" s="4"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -19505,7 +19505,7 @@
       <c r="BD735" s="4"/>
       <c r="BE735" s="4"/>
     </row>
-    <row r="736" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A736" s="4"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -19529,7 +19529,7 @@
       <c r="BD736" s="4"/>
       <c r="BE736" s="4"/>
     </row>
-    <row r="737" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A737" s="4"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -19553,7 +19553,7 @@
       <c r="BD737" s="4"/>
       <c r="BE737" s="4"/>
     </row>
-    <row r="738" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A738" s="4"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -19577,7 +19577,7 @@
       <c r="BD738" s="4"/>
       <c r="BE738" s="4"/>
     </row>
-    <row r="739" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A739" s="4"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -19601,7 +19601,7 @@
       <c r="BD739" s="4"/>
       <c r="BE739" s="4"/>
     </row>
-    <row r="740" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A740" s="4"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -19625,7 +19625,7 @@
       <c r="BD740" s="4"/>
       <c r="BE740" s="4"/>
     </row>
-    <row r="741" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A741" s="4"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -19649,7 +19649,7 @@
       <c r="BD741" s="4"/>
       <c r="BE741" s="4"/>
     </row>
-    <row r="742" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="4"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -19673,7 +19673,7 @@
       <c r="BD742" s="4"/>
       <c r="BE742" s="4"/>
     </row>
-    <row r="743" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="4"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -19697,7 +19697,7 @@
       <c r="BD743" s="4"/>
       <c r="BE743" s="4"/>
     </row>
-    <row r="744" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="4"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -19721,7 +19721,7 @@
       <c r="BD744" s="4"/>
       <c r="BE744" s="4"/>
     </row>
-    <row r="745" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A745" s="4"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -19745,7 +19745,7 @@
       <c r="BD745" s="4"/>
       <c r="BE745" s="4"/>
     </row>
-    <row r="746" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A746" s="4"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -19769,7 +19769,7 @@
       <c r="BD746" s="4"/>
       <c r="BE746" s="4"/>
     </row>
-    <row r="747" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A747" s="4"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -19793,7 +19793,7 @@
       <c r="BD747" s="4"/>
       <c r="BE747" s="4"/>
     </row>
-    <row r="748" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A748" s="4"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -19817,7 +19817,7 @@
       <c r="BD748" s="4"/>
       <c r="BE748" s="4"/>
     </row>
-    <row r="749" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A749" s="4"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -19841,7 +19841,7 @@
       <c r="BD749" s="4"/>
       <c r="BE749" s="4"/>
     </row>
-    <row r="750" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A750" s="4"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -19865,7 +19865,7 @@
       <c r="BD750" s="4"/>
       <c r="BE750" s="4"/>
     </row>
-    <row r="751" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A751" s="4"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
@@ -19889,7 +19889,7 @@
       <c r="BD751" s="4"/>
       <c r="BE751" s="4"/>
     </row>
-    <row r="752" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A752" s="4"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
@@ -19913,7 +19913,7 @@
       <c r="BD752" s="4"/>
       <c r="BE752" s="4"/>
     </row>
-    <row r="753" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A753" s="4"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
@@ -19937,7 +19937,7 @@
       <c r="BD753" s="4"/>
       <c r="BE753" s="4"/>
     </row>
-    <row r="754" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A754" s="4"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
@@ -19961,7 +19961,7 @@
       <c r="BD754" s="4"/>
       <c r="BE754" s="4"/>
     </row>
-    <row r="755" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A755" s="4"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
@@ -19985,7 +19985,7 @@
       <c r="BD755" s="4"/>
       <c r="BE755" s="4"/>
     </row>
-    <row r="756" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A756" s="4"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
@@ -20009,7 +20009,7 @@
       <c r="BD756" s="4"/>
       <c r="BE756" s="4"/>
     </row>
-    <row r="757" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A757" s="4"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
@@ -20033,7 +20033,7 @@
       <c r="BD757" s="4"/>
       <c r="BE757" s="4"/>
     </row>
-    <row r="758" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A758" s="4"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
@@ -20057,7 +20057,7 @@
       <c r="BD758" s="4"/>
       <c r="BE758" s="4"/>
     </row>
-    <row r="759" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A759" s="4"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
@@ -20081,7 +20081,7 @@
       <c r="BD759" s="4"/>
       <c r="BE759" s="4"/>
     </row>
-    <row r="760" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A760" s="4"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
@@ -20105,7 +20105,7 @@
       <c r="BD760" s="4"/>
       <c r="BE760" s="4"/>
     </row>
-    <row r="761" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A761" s="4"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
@@ -20129,7 +20129,7 @@
       <c r="BD761" s="4"/>
       <c r="BE761" s="4"/>
     </row>
-    <row r="762" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A762" s="4"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
@@ -20153,7 +20153,7 @@
       <c r="BD762" s="4"/>
       <c r="BE762" s="4"/>
     </row>
-    <row r="763" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A763" s="4"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
@@ -20177,7 +20177,7 @@
       <c r="BD763" s="4"/>
       <c r="BE763" s="4"/>
     </row>
-    <row r="764" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A764" s="4"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
@@ -20201,7 +20201,7 @@
       <c r="BD764" s="4"/>
       <c r="BE764" s="4"/>
     </row>
-    <row r="765" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A765" s="4"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
@@ -20225,7 +20225,7 @@
       <c r="BD765" s="4"/>
       <c r="BE765" s="4"/>
     </row>
-    <row r="766" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A766" s="4"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
@@ -20249,7 +20249,7 @@
       <c r="BD766" s="4"/>
       <c r="BE766" s="4"/>
     </row>
-    <row r="767" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A767" s="4"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
@@ -20273,7 +20273,7 @@
       <c r="BD767" s="4"/>
       <c r="BE767" s="4"/>
     </row>
-    <row r="768" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A768" s="4"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
@@ -20297,7 +20297,7 @@
       <c r="BD768" s="4"/>
       <c r="BE768" s="4"/>
     </row>
-    <row r="769" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A769" s="4"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
@@ -20321,7 +20321,7 @@
       <c r="BD769" s="4"/>
       <c r="BE769" s="4"/>
     </row>
-    <row r="770" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A770" s="4"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
@@ -20345,7 +20345,7 @@
       <c r="BD770" s="4"/>
       <c r="BE770" s="4"/>
     </row>
-    <row r="771" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A771" s="4"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
@@ -20369,7 +20369,7 @@
       <c r="BD771" s="4"/>
       <c r="BE771" s="4"/>
     </row>
-    <row r="772" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A772" s="4"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
@@ -20393,7 +20393,7 @@
       <c r="BD772" s="4"/>
       <c r="BE772" s="4"/>
     </row>
-    <row r="773" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A773" s="4"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
@@ -20417,7 +20417,7 @@
       <c r="BD773" s="4"/>
       <c r="BE773" s="4"/>
     </row>
-    <row r="774" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A774" s="4"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
@@ -20441,7 +20441,7 @@
       <c r="BD774" s="4"/>
       <c r="BE774" s="4"/>
     </row>
-    <row r="775" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A775" s="4"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
@@ -20465,7 +20465,7 @@
       <c r="BD775" s="4"/>
       <c r="BE775" s="4"/>
     </row>
-    <row r="776" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A776" s="4"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
@@ -20489,7 +20489,7 @@
       <c r="BD776" s="4"/>
       <c r="BE776" s="4"/>
     </row>
-    <row r="777" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A777" s="4"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
@@ -20513,7 +20513,7 @@
       <c r="BD777" s="4"/>
       <c r="BE777" s="4"/>
     </row>
-    <row r="778" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A778" s="4"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
@@ -20537,7 +20537,7 @@
       <c r="BD778" s="4"/>
       <c r="BE778" s="4"/>
     </row>
-    <row r="779" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A779" s="4"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
@@ -20561,7 +20561,7 @@
       <c r="BD779" s="4"/>
       <c r="BE779" s="4"/>
     </row>
-    <row r="780" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A780" s="4"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
@@ -20585,7 +20585,7 @@
       <c r="BD780" s="4"/>
       <c r="BE780" s="4"/>
     </row>
-    <row r="781" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A781" s="4"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
@@ -20609,7 +20609,7 @@
       <c r="BD781" s="4"/>
       <c r="BE781" s="4"/>
     </row>
-    <row r="782" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A782" s="4"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
@@ -20633,7 +20633,7 @@
       <c r="BD782" s="4"/>
       <c r="BE782" s="4"/>
     </row>
-    <row r="783" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A783" s="4"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
@@ -20657,7 +20657,7 @@
       <c r="BD783" s="4"/>
       <c r="BE783" s="4"/>
     </row>
-    <row r="784" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A784" s="4"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
@@ -20681,7 +20681,7 @@
       <c r="BD784" s="4"/>
       <c r="BE784" s="4"/>
     </row>
-    <row r="785" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A785" s="4"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
@@ -20705,7 +20705,7 @@
       <c r="BD785" s="4"/>
       <c r="BE785" s="4"/>
     </row>
-    <row r="786" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A786" s="4"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
@@ -20729,7 +20729,7 @@
       <c r="BD786" s="4"/>
       <c r="BE786" s="4"/>
     </row>
-    <row r="787" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A787" s="4"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
@@ -20753,7 +20753,7 @@
       <c r="BD787" s="4"/>
       <c r="BE787" s="4"/>
     </row>
-    <row r="788" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A788" s="4"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
@@ -20777,7 +20777,7 @@
       <c r="BD788" s="4"/>
       <c r="BE788" s="4"/>
     </row>
-    <row r="789" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A789" s="4"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
@@ -20801,7 +20801,7 @@
       <c r="BD789" s="4"/>
       <c r="BE789" s="4"/>
     </row>
-    <row r="790" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A790" s="4"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
@@ -20825,7 +20825,7 @@
       <c r="BD790" s="4"/>
       <c r="BE790" s="4"/>
     </row>
-    <row r="791" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A791" s="4"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
@@ -20849,7 +20849,7 @@
       <c r="BD791" s="4"/>
       <c r="BE791" s="4"/>
     </row>
-    <row r="792" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A792" s="4"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
@@ -20873,7 +20873,7 @@
       <c r="BD792" s="4"/>
       <c r="BE792" s="4"/>
     </row>
-    <row r="793" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A793" s="4"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
@@ -20897,7 +20897,7 @@
       <c r="BD793" s="4"/>
       <c r="BE793" s="4"/>
     </row>
-    <row r="794" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A794" s="4"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
@@ -20921,7 +20921,7 @@
       <c r="BD794" s="4"/>
       <c r="BE794" s="4"/>
     </row>
-    <row r="795" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A795" s="4"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
@@ -20945,7 +20945,7 @@
       <c r="BD795" s="4"/>
       <c r="BE795" s="4"/>
     </row>
-    <row r="796" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A796" s="4"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
@@ -20969,7 +20969,7 @@
       <c r="BD796" s="4"/>
       <c r="BE796" s="4"/>
     </row>
-    <row r="797" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A797" s="4"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
@@ -20993,7 +20993,7 @@
       <c r="BD797" s="4"/>
       <c r="BE797" s="4"/>
     </row>
-    <row r="798" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A798" s="4"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
@@ -21017,7 +21017,7 @@
       <c r="BD798" s="4"/>
       <c r="BE798" s="4"/>
     </row>
-    <row r="799" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A799" s="4"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
@@ -21041,7 +21041,7 @@
       <c r="BD799" s="4"/>
       <c r="BE799" s="4"/>
     </row>
-    <row r="800" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A800" s="4"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
@@ -21065,7 +21065,7 @@
       <c r="BD800" s="4"/>
       <c r="BE800" s="4"/>
     </row>
-    <row r="801" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A801" s="4"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
@@ -21089,7 +21089,7 @@
       <c r="BD801" s="4"/>
       <c r="BE801" s="4"/>
     </row>
-    <row r="802" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A802" s="4"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
@@ -21113,7 +21113,7 @@
       <c r="BD802" s="4"/>
       <c r="BE802" s="4"/>
     </row>
-    <row r="803" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A803" s="4"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
@@ -21137,7 +21137,7 @@
       <c r="BD803" s="4"/>
       <c r="BE803" s="4"/>
     </row>
-    <row r="804" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A804" s="4"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
@@ -21161,7 +21161,7 @@
       <c r="BD804" s="4"/>
       <c r="BE804" s="4"/>
     </row>
-    <row r="805" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A805" s="4"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
@@ -21185,7 +21185,7 @@
       <c r="BD805" s="4"/>
       <c r="BE805" s="4"/>
     </row>
-    <row r="806" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A806" s="4"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
@@ -21209,7 +21209,7 @@
       <c r="BD806" s="4"/>
       <c r="BE806" s="4"/>
     </row>
-    <row r="807" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A807" s="4"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
@@ -21233,7 +21233,7 @@
       <c r="BD807" s="4"/>
       <c r="BE807" s="4"/>
     </row>
-    <row r="808" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A808" s="4"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
@@ -21257,7 +21257,7 @@
       <c r="BD808" s="4"/>
       <c r="BE808" s="4"/>
     </row>
-    <row r="809" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A809" s="4"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
@@ -21281,7 +21281,7 @@
       <c r="BD809" s="4"/>
       <c r="BE809" s="4"/>
     </row>
-    <row r="810" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A810" s="4"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
@@ -21305,7 +21305,7 @@
       <c r="BD810" s="4"/>
       <c r="BE810" s="4"/>
     </row>
-    <row r="811" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A811" s="4"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
@@ -21329,7 +21329,7 @@
       <c r="BD811" s="4"/>
       <c r="BE811" s="4"/>
     </row>
-    <row r="812" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A812" s="4"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
@@ -21353,7 +21353,7 @@
       <c r="BD812" s="4"/>
       <c r="BE812" s="4"/>
     </row>
-    <row r="813" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A813" s="4"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
@@ -21377,7 +21377,7 @@
       <c r="BD813" s="4"/>
       <c r="BE813" s="4"/>
     </row>
-    <row r="814" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A814" s="4"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
@@ -21401,7 +21401,7 @@
       <c r="BD814" s="4"/>
       <c r="BE814" s="4"/>
     </row>
-    <row r="815" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A815" s="4"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
@@ -21425,7 +21425,7 @@
       <c r="BD815" s="4"/>
       <c r="BE815" s="4"/>
     </row>
-    <row r="816" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A816" s="4"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
@@ -21449,7 +21449,7 @@
       <c r="BD816" s="4"/>
       <c r="BE816" s="4"/>
     </row>
-    <row r="817" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A817" s="4"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
@@ -21473,7 +21473,7 @@
       <c r="BD817" s="4"/>
       <c r="BE817" s="4"/>
     </row>
-    <row r="818" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A818" s="4"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
@@ -21497,7 +21497,7 @@
       <c r="BD818" s="4"/>
       <c r="BE818" s="4"/>
     </row>
-    <row r="819" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A819" s="4"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
@@ -21521,7 +21521,7 @@
       <c r="BD819" s="4"/>
       <c r="BE819" s="4"/>
     </row>
-    <row r="820" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A820" s="4"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
@@ -21545,7 +21545,7 @@
       <c r="BD820" s="4"/>
       <c r="BE820" s="4"/>
     </row>
-    <row r="821" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A821" s="4"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
@@ -21569,7 +21569,7 @@
       <c r="BD821" s="4"/>
       <c r="BE821" s="4"/>
     </row>
-    <row r="822" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A822" s="4"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
@@ -21593,7 +21593,7 @@
       <c r="BD822" s="4"/>
       <c r="BE822" s="4"/>
     </row>
-    <row r="823" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A823" s="4"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
@@ -21617,7 +21617,7 @@
       <c r="BD823" s="4"/>
       <c r="BE823" s="4"/>
     </row>
-    <row r="824" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A824" s="4"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
@@ -21641,7 +21641,7 @@
       <c r="BD824" s="4"/>
       <c r="BE824" s="4"/>
     </row>
-    <row r="825" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A825" s="4"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
@@ -21665,7 +21665,7 @@
       <c r="BD825" s="4"/>
       <c r="BE825" s="4"/>
     </row>
-    <row r="826" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A826" s="4"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
@@ -21689,7 +21689,7 @@
       <c r="BD826" s="4"/>
       <c r="BE826" s="4"/>
     </row>
-    <row r="827" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A827" s="4"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
@@ -21713,7 +21713,7 @@
       <c r="BD827" s="4"/>
       <c r="BE827" s="4"/>
     </row>
-    <row r="828" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A828" s="4"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
@@ -21737,7 +21737,7 @@
       <c r="BD828" s="4"/>
       <c r="BE828" s="4"/>
     </row>
-    <row r="829" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A829" s="4"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
@@ -21761,7 +21761,7 @@
       <c r="BD829" s="4"/>
       <c r="BE829" s="4"/>
     </row>
-    <row r="830" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A830" s="4"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -21785,7 +21785,7 @@
       <c r="BD830" s="4"/>
       <c r="BE830" s="4"/>
     </row>
-    <row r="831" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A831" s="4"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
@@ -21809,7 +21809,7 @@
       <c r="BD831" s="4"/>
       <c r="BE831" s="4"/>
     </row>
-    <row r="832" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A832" s="4"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
@@ -21833,7 +21833,7 @@
       <c r="BD832" s="4"/>
       <c r="BE832" s="4"/>
     </row>
-    <row r="833" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A833" s="4"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
@@ -21857,7 +21857,7 @@
       <c r="BD833" s="4"/>
       <c r="BE833" s="4"/>
     </row>
-    <row r="834" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A834" s="4"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
@@ -21881,7 +21881,7 @@
       <c r="BD834" s="4"/>
       <c r="BE834" s="4"/>
     </row>
-    <row r="835" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A835" s="4"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
@@ -21905,7 +21905,7 @@
       <c r="BD835" s="4"/>
       <c r="BE835" s="4"/>
     </row>
-    <row r="836" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A836" s="4"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
@@ -21929,7 +21929,7 @@
       <c r="BD836" s="4"/>
       <c r="BE836" s="4"/>
     </row>
-    <row r="837" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A837" s="4"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
@@ -21953,7 +21953,7 @@
       <c r="BD837" s="4"/>
       <c r="BE837" s="4"/>
     </row>
-    <row r="838" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A838" s="4"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
@@ -21977,7 +21977,7 @@
       <c r="BD838" s="4"/>
       <c r="BE838" s="4"/>
     </row>
-    <row r="839" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A839" s="4"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
@@ -22001,7 +22001,7 @@
       <c r="BD839" s="4"/>
       <c r="BE839" s="4"/>
     </row>
-    <row r="840" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A840" s="4"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
@@ -22025,7 +22025,7 @@
       <c r="BD840" s="4"/>
       <c r="BE840" s="4"/>
     </row>
-    <row r="841" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A841" s="4"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
@@ -22049,7 +22049,7 @@
       <c r="BD841" s="4"/>
       <c r="BE841" s="4"/>
     </row>
-    <row r="842" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A842" s="4"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
@@ -22073,7 +22073,7 @@
       <c r="BD842" s="4"/>
       <c r="BE842" s="4"/>
     </row>
-    <row r="843" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A843" s="4"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
@@ -22097,7 +22097,7 @@
       <c r="BD843" s="4"/>
       <c r="BE843" s="4"/>
     </row>
-    <row r="844" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A844" s="4"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
@@ -22121,7 +22121,7 @@
       <c r="BD844" s="4"/>
       <c r="BE844" s="4"/>
     </row>
-    <row r="845" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A845" s="4"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
@@ -22145,7 +22145,7 @@
       <c r="BD845" s="4"/>
       <c r="BE845" s="4"/>
     </row>
-    <row r="846" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A846" s="4"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
@@ -22169,7 +22169,7 @@
       <c r="BD846" s="4"/>
       <c r="BE846" s="4"/>
     </row>
-    <row r="847" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A847" s="4"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
@@ -22193,7 +22193,7 @@
       <c r="BD847" s="4"/>
       <c r="BE847" s="4"/>
     </row>
-    <row r="848" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A848" s="4"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
@@ -22217,7 +22217,7 @@
       <c r="BD848" s="4"/>
       <c r="BE848" s="4"/>
     </row>
-    <row r="849" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A849" s="4"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
@@ -22241,7 +22241,7 @@
       <c r="BD849" s="4"/>
       <c r="BE849" s="4"/>
     </row>
-    <row r="850" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A850" s="4"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
@@ -22265,7 +22265,7 @@
       <c r="BD850" s="4"/>
       <c r="BE850" s="4"/>
     </row>
-    <row r="851" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A851" s="4"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
@@ -22289,7 +22289,7 @@
       <c r="BD851" s="4"/>
       <c r="BE851" s="4"/>
     </row>
-    <row r="852" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A852" s="4"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
@@ -22313,7 +22313,7 @@
       <c r="BD852" s="4"/>
       <c r="BE852" s="4"/>
     </row>
-    <row r="853" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A853" s="4"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
@@ -22337,7 +22337,7 @@
       <c r="BD853" s="4"/>
       <c r="BE853" s="4"/>
     </row>
-    <row r="854" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A854" s="4"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
@@ -22361,7 +22361,7 @@
       <c r="BD854" s="4"/>
       <c r="BE854" s="4"/>
     </row>
-    <row r="855" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A855" s="4"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
@@ -22385,7 +22385,7 @@
       <c r="BD855" s="4"/>
       <c r="BE855" s="4"/>
     </row>
-    <row r="856" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A856" s="4"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
@@ -22409,7 +22409,7 @@
       <c r="BD856" s="4"/>
       <c r="BE856" s="4"/>
     </row>
-    <row r="857" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A857" s="4"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
@@ -22433,7 +22433,7 @@
       <c r="BD857" s="4"/>
       <c r="BE857" s="4"/>
     </row>
-    <row r="858" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A858" s="4"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -22457,7 +22457,7 @@
       <c r="BD858" s="4"/>
       <c r="BE858" s="4"/>
     </row>
-    <row r="859" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A859" s="4"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
@@ -22481,7 +22481,7 @@
       <c r="BD859" s="4"/>
       <c r="BE859" s="4"/>
     </row>
-    <row r="860" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A860" s="4"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
@@ -22505,7 +22505,7 @@
       <c r="BD860" s="4"/>
       <c r="BE860" s="4"/>
     </row>
-    <row r="861" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A861" s="4"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
@@ -22529,7 +22529,7 @@
       <c r="BD861" s="4"/>
       <c r="BE861" s="4"/>
     </row>
-    <row r="862" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A862" s="4"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
@@ -22553,7 +22553,7 @@
       <c r="BD862" s="4"/>
       <c r="BE862" s="4"/>
     </row>
-    <row r="863" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A863" s="4"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
@@ -22577,7 +22577,7 @@
       <c r="BD863" s="4"/>
       <c r="BE863" s="4"/>
     </row>
-    <row r="864" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A864" s="4"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
@@ -22601,7 +22601,7 @@
       <c r="BD864" s="4"/>
       <c r="BE864" s="4"/>
     </row>
-    <row r="865" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A865" s="4"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
@@ -22625,7 +22625,7 @@
       <c r="BD865" s="4"/>
       <c r="BE865" s="4"/>
     </row>
-    <row r="866" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A866" s="4"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
@@ -22649,7 +22649,7 @@
       <c r="BD866" s="4"/>
       <c r="BE866" s="4"/>
     </row>
-    <row r="867" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A867" s="4"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
@@ -22673,7 +22673,7 @@
       <c r="BD867" s="4"/>
       <c r="BE867" s="4"/>
     </row>
-    <row r="868" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A868" s="4"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
@@ -22697,7 +22697,7 @@
       <c r="BD868" s="4"/>
       <c r="BE868" s="4"/>
     </row>
-    <row r="869" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A869" s="4"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
@@ -22721,7 +22721,7 @@
       <c r="BD869" s="4"/>
       <c r="BE869" s="4"/>
     </row>
-    <row r="870" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A870" s="4"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
@@ -22745,7 +22745,7 @@
       <c r="BD870" s="4"/>
       <c r="BE870" s="4"/>
     </row>
-    <row r="871" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A871" s="4"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
@@ -22769,7 +22769,7 @@
       <c r="BD871" s="4"/>
       <c r="BE871" s="4"/>
     </row>
-    <row r="872" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A872" s="4"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
@@ -22793,7 +22793,7 @@
       <c r="BD872" s="4"/>
       <c r="BE872" s="4"/>
     </row>
-    <row r="873" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A873" s="4"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
@@ -22817,7 +22817,7 @@
       <c r="BD873" s="4"/>
       <c r="BE873" s="4"/>
     </row>
-    <row r="874" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A874" s="4"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
@@ -22841,7 +22841,7 @@
       <c r="BD874" s="4"/>
       <c r="BE874" s="4"/>
     </row>
-    <row r="875" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A875" s="4"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
@@ -22865,7 +22865,7 @@
       <c r="BD875" s="4"/>
       <c r="BE875" s="4"/>
     </row>
-    <row r="876" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A876" s="4"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
@@ -22889,7 +22889,7 @@
       <c r="BD876" s="4"/>
       <c r="BE876" s="4"/>
     </row>
-    <row r="877" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A877" s="4"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
@@ -22913,7 +22913,7 @@
       <c r="BD877" s="4"/>
       <c r="BE877" s="4"/>
     </row>
-    <row r="878" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A878" s="4"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
@@ -22937,7 +22937,7 @@
       <c r="BD878" s="4"/>
       <c r="BE878" s="4"/>
     </row>
-    <row r="879" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A879" s="4"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
@@ -22961,7 +22961,7 @@
       <c r="BD879" s="4"/>
       <c r="BE879" s="4"/>
     </row>
-    <row r="880" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A880" s="4"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
@@ -22985,7 +22985,7 @@
       <c r="BD880" s="4"/>
       <c r="BE880" s="4"/>
     </row>
-    <row r="881" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A881" s="4"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
@@ -23009,7 +23009,7 @@
       <c r="BD881" s="4"/>
       <c r="BE881" s="4"/>
     </row>
-    <row r="882" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A882" s="4"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
@@ -23033,7 +23033,7 @@
       <c r="BD882" s="4"/>
       <c r="BE882" s="4"/>
     </row>
-    <row r="883" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A883" s="4"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
@@ -23057,7 +23057,7 @@
       <c r="BD883" s="4"/>
       <c r="BE883" s="4"/>
     </row>
-    <row r="884" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A884" s="4"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
@@ -23081,7 +23081,7 @@
       <c r="BD884" s="4"/>
       <c r="BE884" s="4"/>
     </row>
-    <row r="885" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A885" s="4"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
@@ -23105,7 +23105,7 @@
       <c r="BD885" s="4"/>
       <c r="BE885" s="4"/>
     </row>
-    <row r="886" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A886" s="4"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -23129,7 +23129,7 @@
       <c r="BD886" s="4"/>
       <c r="BE886" s="4"/>
     </row>
-    <row r="887" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A887" s="4"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
@@ -23153,7 +23153,7 @@
       <c r="BD887" s="4"/>
       <c r="BE887" s="4"/>
     </row>
-    <row r="888" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A888" s="4"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
@@ -23177,7 +23177,7 @@
       <c r="BD888" s="4"/>
       <c r="BE888" s="4"/>
     </row>
-    <row r="889" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A889" s="4"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
@@ -23201,7 +23201,7 @@
       <c r="BD889" s="4"/>
       <c r="BE889" s="4"/>
     </row>
-    <row r="890" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A890" s="4"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
@@ -23225,7 +23225,7 @@
       <c r="BD890" s="4"/>
       <c r="BE890" s="4"/>
     </row>
-    <row r="891" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A891" s="4"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
@@ -23249,7 +23249,7 @@
       <c r="BD891" s="4"/>
       <c r="BE891" s="4"/>
     </row>
-    <row r="892" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A892" s="4"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
@@ -23273,7 +23273,7 @@
       <c r="BD892" s="4"/>
       <c r="BE892" s="4"/>
     </row>
-    <row r="893" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A893" s="4"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
@@ -23297,7 +23297,7 @@
       <c r="BD893" s="4"/>
       <c r="BE893" s="4"/>
     </row>
-    <row r="894" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A894" s="4"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
@@ -23321,7 +23321,7 @@
       <c r="BD894" s="4"/>
       <c r="BE894" s="4"/>
     </row>
-    <row r="895" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A895" s="4"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
@@ -23345,7 +23345,7 @@
       <c r="BD895" s="4"/>
       <c r="BE895" s="4"/>
     </row>
-    <row r="896" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A896" s="4"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
@@ -23369,7 +23369,7 @@
       <c r="BD896" s="4"/>
       <c r="BE896" s="4"/>
     </row>
-    <row r="897" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A897" s="4"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
@@ -23393,7 +23393,7 @@
       <c r="BD897" s="4"/>
       <c r="BE897" s="4"/>
     </row>
-    <row r="898" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A898" s="4"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
@@ -23417,7 +23417,7 @@
       <c r="BD898" s="4"/>
       <c r="BE898" s="4"/>
     </row>
-    <row r="899" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A899" s="4"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
@@ -23441,7 +23441,7 @@
       <c r="BD899" s="4"/>
       <c r="BE899" s="4"/>
     </row>
-    <row r="900" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A900" s="4"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
@@ -23465,7 +23465,7 @@
       <c r="BD900" s="4"/>
       <c r="BE900" s="4"/>
     </row>
-    <row r="901" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A901" s="4"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
@@ -23489,7 +23489,7 @@
       <c r="BD901" s="4"/>
       <c r="BE901" s="4"/>
     </row>
-    <row r="902" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A902" s="4"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
@@ -23513,7 +23513,7 @@
       <c r="BD902" s="4"/>
       <c r="BE902" s="4"/>
     </row>
-    <row r="903" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A903" s="4"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
@@ -23537,7 +23537,7 @@
       <c r="BD903" s="4"/>
       <c r="BE903" s="4"/>
     </row>
-    <row r="904" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A904" s="4"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
@@ -23561,7 +23561,7 @@
       <c r="BD904" s="4"/>
       <c r="BE904" s="4"/>
     </row>
-    <row r="905" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A905" s="4"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
@@ -23585,7 +23585,7 @@
       <c r="BD905" s="4"/>
       <c r="BE905" s="4"/>
     </row>
-    <row r="906" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A906" s="4"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
@@ -23609,7 +23609,7 @@
       <c r="BD906" s="4"/>
       <c r="BE906" s="4"/>
     </row>
-    <row r="907" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A907" s="4"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
@@ -23633,7 +23633,7 @@
       <c r="BD907" s="4"/>
       <c r="BE907" s="4"/>
     </row>
-    <row r="908" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A908" s="4"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
@@ -23657,7 +23657,7 @@
       <c r="BD908" s="4"/>
       <c r="BE908" s="4"/>
     </row>
-    <row r="909" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A909" s="4"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
@@ -23681,7 +23681,7 @@
       <c r="BD909" s="4"/>
       <c r="BE909" s="4"/>
     </row>
-    <row r="910" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A910" s="4"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
@@ -23705,7 +23705,7 @@
       <c r="BD910" s="4"/>
       <c r="BE910" s="4"/>
     </row>
-    <row r="911" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A911" s="4"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
@@ -23729,7 +23729,7 @@
       <c r="BD911" s="4"/>
       <c r="BE911" s="4"/>
     </row>
-    <row r="912" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A912" s="4"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
@@ -23753,7 +23753,7 @@
       <c r="BD912" s="4"/>
       <c r="BE912" s="4"/>
     </row>
-    <row r="913" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A913" s="4"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
@@ -23777,7 +23777,7 @@
       <c r="BD913" s="4"/>
       <c r="BE913" s="4"/>
     </row>
-    <row r="914" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A914" s="4"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -23801,7 +23801,7 @@
       <c r="BD914" s="4"/>
       <c r="BE914" s="4"/>
     </row>
-    <row r="915" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A915" s="4"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
@@ -23825,7 +23825,7 @@
       <c r="BD915" s="4"/>
       <c r="BE915" s="4"/>
     </row>
-    <row r="916" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A916" s="4"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
@@ -23849,7 +23849,7 @@
       <c r="BD916" s="4"/>
       <c r="BE916" s="4"/>
     </row>
-    <row r="917" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A917" s="4"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
@@ -23873,7 +23873,7 @@
       <c r="BD917" s="4"/>
       <c r="BE917" s="4"/>
     </row>
-    <row r="918" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A918" s="4"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
@@ -23897,7 +23897,7 @@
       <c r="BD918" s="4"/>
       <c r="BE918" s="4"/>
     </row>
-    <row r="919" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A919" s="4"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
@@ -23921,7 +23921,7 @@
       <c r="BD919" s="4"/>
       <c r="BE919" s="4"/>
     </row>
-    <row r="920" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A920" s="4"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
@@ -23945,7 +23945,7 @@
       <c r="BD920" s="4"/>
       <c r="BE920" s="4"/>
     </row>
-    <row r="921" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A921" s="4"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
@@ -23969,7 +23969,7 @@
       <c r="BD921" s="4"/>
       <c r="BE921" s="4"/>
     </row>
-    <row r="922" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A922" s="4"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
@@ -23993,7 +23993,7 @@
       <c r="BD922" s="4"/>
       <c r="BE922" s="4"/>
     </row>
-    <row r="923" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A923" s="4"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
@@ -24017,7 +24017,7 @@
       <c r="BD923" s="4"/>
       <c r="BE923" s="4"/>
     </row>
-    <row r="924" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A924" s="4"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
@@ -24041,7 +24041,7 @@
       <c r="BD924" s="4"/>
       <c r="BE924" s="4"/>
     </row>
-    <row r="925" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A925" s="4"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
@@ -24065,7 +24065,7 @@
       <c r="BD925" s="4"/>
       <c r="BE925" s="4"/>
     </row>
-    <row r="926" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A926" s="4"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
@@ -24089,7 +24089,7 @@
       <c r="BD926" s="4"/>
       <c r="BE926" s="4"/>
     </row>
-    <row r="927" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A927" s="4"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
@@ -24113,7 +24113,7 @@
       <c r="BD927" s="4"/>
       <c r="BE927" s="4"/>
     </row>
-    <row r="928" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A928" s="4"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
@@ -24137,7 +24137,7 @@
       <c r="BD928" s="4"/>
       <c r="BE928" s="4"/>
     </row>
-    <row r="929" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A929" s="4"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
@@ -24161,7 +24161,7 @@
       <c r="BD929" s="4"/>
       <c r="BE929" s="4"/>
     </row>
-    <row r="930" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A930" s="4"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
@@ -24185,7 +24185,7 @@
       <c r="BD930" s="4"/>
       <c r="BE930" s="4"/>
     </row>
-    <row r="931" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A931" s="4"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
@@ -24209,7 +24209,7 @@
       <c r="BD931" s="4"/>
       <c r="BE931" s="4"/>
     </row>
-    <row r="932" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A932" s="4"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
@@ -24233,7 +24233,7 @@
       <c r="BD932" s="4"/>
       <c r="BE932" s="4"/>
     </row>
-    <row r="933" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A933" s="4"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
@@ -24257,7 +24257,7 @@
       <c r="BD933" s="4"/>
       <c r="BE933" s="4"/>
     </row>
-    <row r="934" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A934" s="4"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
@@ -24281,7 +24281,7 @@
       <c r="BD934" s="4"/>
       <c r="BE934" s="4"/>
     </row>
-    <row r="935" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A935" s="4"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
@@ -24305,7 +24305,7 @@
       <c r="BD935" s="4"/>
       <c r="BE935" s="4"/>
     </row>
-    <row r="936" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A936" s="4"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
@@ -24329,7 +24329,7 @@
       <c r="BD936" s="4"/>
       <c r="BE936" s="4"/>
     </row>
-    <row r="937" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A937" s="4"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
@@ -24353,7 +24353,7 @@
       <c r="BD937" s="4"/>
       <c r="BE937" s="4"/>
     </row>
-    <row r="938" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A938" s="4"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
@@ -24377,7 +24377,7 @@
       <c r="BD938" s="4"/>
       <c r="BE938" s="4"/>
     </row>
-    <row r="939" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A939" s="4"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
@@ -24401,7 +24401,7 @@
       <c r="BD939" s="4"/>
       <c r="BE939" s="4"/>
     </row>
-    <row r="940" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A940" s="4"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
@@ -24425,7 +24425,7 @@
       <c r="BD940" s="4"/>
       <c r="BE940" s="4"/>
     </row>
-    <row r="941" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A941" s="4"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
@@ -24449,7 +24449,7 @@
       <c r="BD941" s="4"/>
       <c r="BE941" s="4"/>
     </row>
-    <row r="942" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A942" s="4"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -24473,7 +24473,7 @@
       <c r="BD942" s="4"/>
       <c r="BE942" s="4"/>
     </row>
-    <row r="943" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A943" s="4"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
@@ -24497,7 +24497,7 @@
       <c r="BD943" s="4"/>
       <c r="BE943" s="4"/>
     </row>
-    <row r="944" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A944" s="4"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
@@ -24521,7 +24521,7 @@
       <c r="BD944" s="4"/>
       <c r="BE944" s="4"/>
     </row>
-    <row r="945" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A945" s="4"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
@@ -24545,7 +24545,7 @@
       <c r="BD945" s="4"/>
       <c r="BE945" s="4"/>
     </row>
-    <row r="946" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A946" s="4"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
@@ -24569,7 +24569,7 @@
       <c r="BD946" s="4"/>
       <c r="BE946" s="4"/>
     </row>
-    <row r="947" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A947" s="4"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
@@ -24593,7 +24593,7 @@
       <c r="BD947" s="4"/>
       <c r="BE947" s="4"/>
     </row>
-    <row r="948" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A948" s="4"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
@@ -24617,7 +24617,7 @@
       <c r="BD948" s="4"/>
       <c r="BE948" s="4"/>
     </row>
-    <row r="949" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A949" s="4"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
@@ -24641,7 +24641,7 @@
       <c r="BD949" s="4"/>
       <c r="BE949" s="4"/>
     </row>
-    <row r="950" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A950" s="4"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
@@ -24665,7 +24665,7 @@
       <c r="BD950" s="4"/>
       <c r="BE950" s="4"/>
     </row>
-    <row r="951" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A951" s="4"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
@@ -24689,7 +24689,7 @@
       <c r="BD951" s="4"/>
       <c r="BE951" s="4"/>
     </row>
-    <row r="952" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A952" s="4"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
@@ -24713,7 +24713,7 @@
       <c r="BD952" s="4"/>
       <c r="BE952" s="4"/>
     </row>
-    <row r="953" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A953" s="4"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
@@ -24737,7 +24737,7 @@
       <c r="BD953" s="4"/>
       <c r="BE953" s="4"/>
     </row>
-    <row r="954" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A954" s="4"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
@@ -24761,7 +24761,7 @@
       <c r="BD954" s="4"/>
       <c r="BE954" s="4"/>
     </row>
-    <row r="955" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A955" s="4"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
@@ -24785,7 +24785,7 @@
       <c r="BD955" s="4"/>
       <c r="BE955" s="4"/>
     </row>
-    <row r="956" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A956" s="4"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
@@ -24809,7 +24809,7 @@
       <c r="BD956" s="4"/>
       <c r="BE956" s="4"/>
     </row>
-    <row r="957" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A957" s="4"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
@@ -24833,7 +24833,7 @@
       <c r="BD957" s="4"/>
       <c r="BE957" s="4"/>
     </row>
-    <row r="958" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A958" s="4"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
@@ -24857,7 +24857,7 @@
       <c r="BD958" s="4"/>
       <c r="BE958" s="4"/>
     </row>
-    <row r="959" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A959" s="4"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
@@ -24881,7 +24881,7 @@
       <c r="BD959" s="4"/>
       <c r="BE959" s="4"/>
     </row>
-    <row r="960" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A960" s="4"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
@@ -24905,7 +24905,7 @@
       <c r="BD960" s="4"/>
       <c r="BE960" s="4"/>
     </row>
-    <row r="961" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A961" s="4"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
@@ -24929,7 +24929,7 @@
       <c r="BD961" s="4"/>
       <c r="BE961" s="4"/>
     </row>
-    <row r="962" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A962" s="4"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
@@ -24953,7 +24953,7 @@
       <c r="BD962" s="4"/>
       <c r="BE962" s="4"/>
     </row>
-    <row r="963" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A963" s="4"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
@@ -24977,7 +24977,7 @@
       <c r="BD963" s="4"/>
       <c r="BE963" s="4"/>
     </row>
-    <row r="964" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A964" s="4"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
@@ -25001,7 +25001,7 @@
       <c r="BD964" s="4"/>
       <c r="BE964" s="4"/>
     </row>
-    <row r="965" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A965" s="4"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
@@ -25025,7 +25025,7 @@
       <c r="BD965" s="4"/>
       <c r="BE965" s="4"/>
     </row>
-    <row r="966" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A966" s="4"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
@@ -25049,7 +25049,7 @@
       <c r="BD966" s="4"/>
       <c r="BE966" s="4"/>
     </row>
-    <row r="967" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A967" s="4"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
@@ -25073,7 +25073,7 @@
       <c r="BD967" s="4"/>
       <c r="BE967" s="4"/>
     </row>
-    <row r="968" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A968" s="4"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
@@ -25097,7 +25097,7 @@
       <c r="BD968" s="4"/>
       <c r="BE968" s="4"/>
     </row>
-    <row r="969" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A969" s="4"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
@@ -25121,7 +25121,7 @@
       <c r="BD969" s="4"/>
       <c r="BE969" s="4"/>
     </row>
-    <row r="970" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A970" s="4"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -25145,7 +25145,7 @@
       <c r="BD970" s="4"/>
       <c r="BE970" s="4"/>
     </row>
-    <row r="971" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A971" s="4"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
@@ -25169,7 +25169,7 @@
       <c r="BD971" s="4"/>
       <c r="BE971" s="4"/>
     </row>
-    <row r="972" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A972" s="4"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
@@ -25193,7 +25193,7 @@
       <c r="BD972" s="4"/>
       <c r="BE972" s="4"/>
     </row>
-    <row r="973" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A973" s="4"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
@@ -25217,7 +25217,7 @@
       <c r="BD973" s="4"/>
       <c r="BE973" s="4"/>
     </row>
-    <row r="974" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A974" s="4"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
@@ -25241,7 +25241,7 @@
       <c r="BD974" s="4"/>
       <c r="BE974" s="4"/>
     </row>
-    <row r="975" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A975" s="4"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
@@ -25265,7 +25265,7 @@
       <c r="BD975" s="4"/>
       <c r="BE975" s="4"/>
     </row>
-    <row r="976" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A976" s="4"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
@@ -25289,7 +25289,7 @@
       <c r="BD976" s="4"/>
       <c r="BE976" s="4"/>
     </row>
-    <row r="977" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A977" s="4"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
@@ -25313,7 +25313,7 @@
       <c r="BD977" s="4"/>
       <c r="BE977" s="4"/>
     </row>
-    <row r="978" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A978" s="4"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
@@ -25337,7 +25337,7 @@
       <c r="BD978" s="4"/>
       <c r="BE978" s="4"/>
     </row>
-    <row r="979" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A979" s="4"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
@@ -25361,7 +25361,7 @@
       <c r="BD979" s="4"/>
       <c r="BE979" s="4"/>
     </row>
-    <row r="980" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A980" s="4"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
@@ -25385,7 +25385,7 @@
       <c r="BD980" s="4"/>
       <c r="BE980" s="4"/>
     </row>
-    <row r="981" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A981" s="4"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
@@ -25409,7 +25409,7 @@
       <c r="BD981" s="4"/>
       <c r="BE981" s="4"/>
     </row>
-    <row r="982" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A982" s="4"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
@@ -25433,7 +25433,7 @@
       <c r="BD982" s="4"/>
       <c r="BE982" s="4"/>
     </row>
-    <row r="983" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A983" s="4"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
@@ -25457,7 +25457,7 @@
       <c r="BD983" s="4"/>
       <c r="BE983" s="4"/>
     </row>
-    <row r="984" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A984" s="4"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
@@ -25481,7 +25481,7 @@
       <c r="BD984" s="4"/>
       <c r="BE984" s="4"/>
     </row>
-    <row r="985" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A985" s="4"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
@@ -25505,7 +25505,7 @@
       <c r="BD985" s="4"/>
       <c r="BE985" s="4"/>
     </row>
-    <row r="986" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A986" s="4"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
@@ -25529,7 +25529,7 @@
       <c r="BD986" s="4"/>
       <c r="BE986" s="4"/>
     </row>
-    <row r="987" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A987" s="4"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
@@ -25553,7 +25553,7 @@
       <c r="BD987" s="4"/>
       <c r="BE987" s="4"/>
     </row>
-    <row r="988" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A988" s="4"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
@@ -25577,7 +25577,7 @@
       <c r="BD988" s="4"/>
       <c r="BE988" s="4"/>
     </row>
-    <row r="989" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A989" s="4"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
@@ -25601,7 +25601,7 @@
       <c r="BD989" s="4"/>
       <c r="BE989" s="4"/>
     </row>
-    <row r="990" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A990" s="4"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
@@ -25625,7 +25625,7 @@
       <c r="BD990" s="4"/>
       <c r="BE990" s="4"/>
     </row>
-    <row r="991" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A991" s="4"/>
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
@@ -25649,7 +25649,7 @@
       <c r="BD991" s="4"/>
       <c r="BE991" s="4"/>
     </row>
-    <row r="992" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A992" s="4"/>
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
@@ -25673,7 +25673,7 @@
       <c r="BD992" s="4"/>
       <c r="BE992" s="4"/>
     </row>
-    <row r="993" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A993" s="4"/>
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
@@ -25697,7 +25697,7 @@
       <c r="BD993" s="4"/>
       <c r="BE993" s="4"/>
     </row>
-    <row r="994" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A994" s="4"/>
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
@@ -25721,7 +25721,7 @@
       <c r="BD994" s="4"/>
       <c r="BE994" s="4"/>
     </row>
-    <row r="995" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A995" s="4"/>
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
@@ -25745,7 +25745,7 @@
       <c r="BD995" s="4"/>
       <c r="BE995" s="4"/>
     </row>
-    <row r="996" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A996" s="4"/>
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
@@ -25769,7 +25769,7 @@
       <c r="BD996" s="4"/>
       <c r="BE996" s="4"/>
     </row>
-    <row r="997" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A997" s="4"/>
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
@@ -25793,7 +25793,7 @@
       <c r="BD997" s="4"/>
       <c r="BE997" s="4"/>
     </row>
-    <row r="998" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A998" s="4"/>
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
@@ -25817,7 +25817,7 @@
       <c r="BD998" s="4"/>
       <c r="BE998" s="4"/>
     </row>
-    <row r="999" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A999" s="4"/>
       <c r="B999" s="4"/>
       <c r="C999" s="4"/>
@@ -25841,7 +25841,7 @@
       <c r="BD999" s="4"/>
       <c r="BE999" s="4"/>
     </row>
-    <row r="1000" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="4"/>
       <c r="B1000" s="4"/>
       <c r="C1000" s="4"/>
@@ -25871,6 +25871,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FD7D29C8E3DCB740B512085BDB890A19" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="252040482c07e84078604bad08e1f478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1998147e-1bae-4425-a5b5-824e2b69f76d" xmlns:ns3="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a426bac492543af192e091bebadc75c6" ns2:_="" ns3:_="">
     <xsd:import namespace="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
@@ -26087,15 +26096,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -26103,6 +26103,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D20EFE-128A-4BEA-B77D-8F21601543E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26117,14 +26125,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
